--- a/research/traditional_assets/database/data/cyprus/cyprus_retail_general.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_retail_general.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1027691527997713</v>
+        <v>0.1026800663587716</v>
       </c>
       <c r="C2">
-        <v>154.8495002729379</v>
+        <v>153.5284137330749</v>
       </c>
       <c r="D2">
-        <v>154.0555002729379</v>
+        <v>154.1804137330749</v>
       </c>
       <c r="E2">
-        <v>-140.9</v>
+        <v>-139.454</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.446</v>
       </c>
       <c r="G2">
         <v>0.794</v>
@@ -1439,28 +1439,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07273379999999999</v>
       </c>
       <c r="N2">
-        <v>12.63333333333333</v>
+        <v>12.56059953333333</v>
       </c>
       <c r="O2">
-        <v>1.579166666666666</v>
+        <v>1.570074941666666</v>
       </c>
       <c r="P2">
-        <v>11.05416666666667</v>
+        <v>10.99052459166666</v>
       </c>
       <c r="Q2">
-        <v>22.95416666666667</v>
+        <v>22.89052459166667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1027691527997713</v>
+        <v>0.1032726680391632</v>
       </c>
       <c r="T2">
-        <v>0.960581759320096</v>
+        <v>0.9690717496171172</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>173.6927444095226</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1026800663587716</v>
+        <v>0.1025909799177718</v>
       </c>
       <c r="C3">
-        <v>153.5284137330749</v>
+        <v>152.2075299257923</v>
       </c>
       <c r="D3">
-        <v>154.1804137330749</v>
+        <v>154.3055299257923</v>
       </c>
       <c r="E3">
-        <v>-139.454</v>
+        <v>-138.008</v>
       </c>
       <c r="F3">
-        <v>1.446</v>
+        <v>2.892</v>
       </c>
       <c r="G3">
         <v>0.794</v>
@@ -1521,28 +1521,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M3">
-        <v>0.07273379999999999</v>
+        <v>0.1454676</v>
       </c>
       <c r="N3">
-        <v>12.56059953333333</v>
+        <v>12.48786573333333</v>
       </c>
       <c r="O3">
-        <v>1.570074941666666</v>
+        <v>1.560983216666666</v>
       </c>
       <c r="P3">
-        <v>10.99052459166666</v>
+        <v>10.92688251666666</v>
       </c>
       <c r="Q3">
-        <v>22.89052459166667</v>
+        <v>22.82688251666666</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1032726680391632</v>
+        <v>0.1037864590997672</v>
       </c>
       <c r="T3">
-        <v>0.9690717496171172</v>
+        <v>0.9777350050222405</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>173.6927444095226</v>
+        <v>86.84637220476129</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1025909799177718</v>
+        <v>0.1025018934767721</v>
       </c>
       <c r="C4">
-        <v>152.2075299257923</v>
+        <v>150.8868493450384</v>
       </c>
       <c r="D4">
-        <v>154.3055299257923</v>
+        <v>154.4308493450384</v>
       </c>
       <c r="E4">
-        <v>-138.008</v>
+        <v>-136.562</v>
       </c>
       <c r="F4">
-        <v>2.892</v>
+        <v>4.338</v>
       </c>
       <c r="G4">
         <v>0.794</v>
@@ -1603,28 +1603,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M4">
-        <v>0.1454676</v>
+        <v>0.2182014</v>
       </c>
       <c r="N4">
-        <v>12.48786573333333</v>
+        <v>12.41513193333333</v>
       </c>
       <c r="O4">
-        <v>1.560983216666666</v>
+        <v>1.551891491666666</v>
       </c>
       <c r="P4">
-        <v>10.92688251666666</v>
+        <v>10.86324044166667</v>
       </c>
       <c r="Q4">
-        <v>22.82688251666666</v>
+        <v>22.76324044166667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1037864590997672</v>
+        <v>0.1043108437904867</v>
       </c>
       <c r="T4">
-        <v>0.9777350050222405</v>
+        <v>0.9865768842501501</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>86.84637220476129</v>
+        <v>57.89758146984085</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1025018934767721</v>
+        <v>0.1024128070357724</v>
       </c>
       <c r="C5">
-        <v>150.8868493450384</v>
+        <v>149.5663724863678</v>
       </c>
       <c r="D5">
-        <v>154.4308493450384</v>
+        <v>154.5563724863678</v>
       </c>
       <c r="E5">
-        <v>-136.562</v>
+        <v>-135.116</v>
       </c>
       <c r="F5">
-        <v>4.338</v>
+        <v>5.784</v>
       </c>
       <c r="G5">
         <v>0.794</v>
@@ -1685,28 +1685,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M5">
-        <v>0.2182014</v>
+        <v>0.2909351999999999</v>
       </c>
       <c r="N5">
-        <v>12.41513193333333</v>
+        <v>12.34239813333333</v>
       </c>
       <c r="O5">
-        <v>1.551891491666666</v>
+        <v>1.542799766666666</v>
       </c>
       <c r="P5">
-        <v>10.86324044166667</v>
+        <v>10.79959836666666</v>
       </c>
       <c r="Q5">
-        <v>22.76324044166667</v>
+        <v>22.69959836666666</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1043108437904867</v>
+        <v>0.1048461531622629</v>
       </c>
       <c r="T5">
-        <v>0.9865768842501501</v>
+        <v>0.9956029692953078</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.89758146984085</v>
+        <v>43.42318610238065</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1024128070357724</v>
+        <v>0.1023237205947727</v>
       </c>
       <c r="C6">
-        <v>149.5663724863678</v>
+        <v>148.2460998469473</v>
       </c>
       <c r="D6">
-        <v>154.5563724863678</v>
+        <v>154.6820998469473</v>
       </c>
       <c r="E6">
-        <v>-135.116</v>
+        <v>-133.67</v>
       </c>
       <c r="F6">
-        <v>5.784</v>
+        <v>7.23</v>
       </c>
       <c r="G6">
         <v>0.794</v>
@@ -1767,28 +1767,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M6">
-        <v>0.2909351999999999</v>
+        <v>0.363669</v>
       </c>
       <c r="N6">
-        <v>12.34239813333333</v>
+        <v>12.26966433333333</v>
       </c>
       <c r="O6">
-        <v>1.542799766666666</v>
+        <v>1.533708041666666</v>
       </c>
       <c r="P6">
-        <v>10.79959836666666</v>
+        <v>10.73595629166666</v>
       </c>
       <c r="Q6">
-        <v>22.69959836666666</v>
+        <v>22.63595629166667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1048461531622629</v>
+        <v>0.1053927322050239</v>
       </c>
       <c r="T6">
-        <v>0.9956029692953078</v>
+        <v>1.004819077183521</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.42318610238065</v>
+        <v>34.73854888190451</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1023237205947727</v>
+        <v>0.102234634153773</v>
       </c>
       <c r="C7">
-        <v>148.2460998469473</v>
+        <v>146.926031925563</v>
       </c>
       <c r="D7">
-        <v>154.6820998469473</v>
+        <v>154.808031925563</v>
       </c>
       <c r="E7">
-        <v>-133.67</v>
+        <v>-132.224</v>
       </c>
       <c r="F7">
-        <v>7.23</v>
+        <v>8.676</v>
       </c>
       <c r="G7">
         <v>0.794</v>
@@ -1849,28 +1849,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M7">
-        <v>0.363669</v>
+        <v>0.4364028</v>
       </c>
       <c r="N7">
-        <v>12.26966433333333</v>
+        <v>12.19693053333333</v>
       </c>
       <c r="O7">
-        <v>1.533708041666666</v>
+        <v>1.524616316666666</v>
       </c>
       <c r="P7">
-        <v>10.73595629166666</v>
+        <v>10.67231421666667</v>
       </c>
       <c r="Q7">
-        <v>22.63595629166667</v>
+        <v>22.57231421666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1053927322050239</v>
+        <v>0.1059509405891202</v>
       </c>
       <c r="T7">
-        <v>1.004819077183521</v>
+        <v>1.014231272473612</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.73854888190451</v>
+        <v>28.94879073492043</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.102234634153773</v>
+        <v>0.1021455477127733</v>
       </c>
       <c r="C8">
-        <v>146.926031925563</v>
+        <v>145.6061692226266</v>
       </c>
       <c r="D8">
-        <v>154.808031925563</v>
+        <v>154.9341692226265</v>
       </c>
       <c r="E8">
-        <v>-132.224</v>
+        <v>-130.778</v>
       </c>
       <c r="F8">
-        <v>8.676</v>
+        <v>10.122</v>
       </c>
       <c r="G8">
         <v>0.794</v>
@@ -1931,28 +1931,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M8">
-        <v>0.4364028</v>
+        <v>0.5091365999999998</v>
       </c>
       <c r="N8">
-        <v>12.19693053333333</v>
+        <v>12.12419673333333</v>
       </c>
       <c r="O8">
-        <v>1.524616316666666</v>
+        <v>1.515524591666666</v>
       </c>
       <c r="P8">
-        <v>10.67231421666667</v>
+        <v>10.60867214166666</v>
       </c>
       <c r="Q8">
-        <v>22.57231421666667</v>
+        <v>22.50867214166666</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1059509405891202</v>
+        <v>0.1065211534545949</v>
       </c>
       <c r="T8">
-        <v>1.014231272473612</v>
+        <v>1.02384588056564</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.94879073492043</v>
+        <v>24.81324920136037</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1021455477127733</v>
+        <v>0.1020564612717736</v>
       </c>
       <c r="C9">
-        <v>145.6061692226266</v>
+        <v>144.2865122401818</v>
       </c>
       <c r="D9">
-        <v>154.9341692226266</v>
+        <v>155.0605122401818</v>
       </c>
       <c r="E9">
-        <v>-130.778</v>
+        <v>-129.332</v>
       </c>
       <c r="F9">
-        <v>10.122</v>
+        <v>11.568</v>
       </c>
       <c r="G9">
         <v>0.794</v>
@@ -2013,28 +2013,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M9">
-        <v>0.5091365999999999</v>
+        <v>0.5818703999999999</v>
       </c>
       <c r="N9">
-        <v>12.12419673333333</v>
+        <v>12.05146293333333</v>
       </c>
       <c r="O9">
-        <v>1.515524591666666</v>
+        <v>1.506432866666666</v>
       </c>
       <c r="P9">
-        <v>10.60867214166666</v>
+        <v>10.54503006666667</v>
       </c>
       <c r="Q9">
-        <v>22.50867214166666</v>
+        <v>22.44503006666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1065211534545949</v>
+        <v>0.1071037622519278</v>
       </c>
       <c r="T9">
-        <v>1.02384588056564</v>
+        <v>1.03366950187706</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.81324920136037</v>
+        <v>21.71159305119032</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1020564612717736</v>
+        <v>0.1019673748307739</v>
       </c>
       <c r="C10">
-        <v>144.2865122401818</v>
+        <v>142.9670614819116</v>
       </c>
       <c r="D10">
-        <v>155.0605122401818</v>
+        <v>155.1870614819116</v>
       </c>
       <c r="E10">
-        <v>-129.332</v>
+        <v>-127.886</v>
       </c>
       <c r="F10">
-        <v>11.568</v>
+        <v>13.014</v>
       </c>
       <c r="G10">
         <v>0.794</v>
@@ -2095,28 +2095,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M10">
-        <v>0.5818703999999999</v>
+        <v>0.6546042</v>
       </c>
       <c r="N10">
-        <v>12.05146293333333</v>
+        <v>11.97872913333333</v>
       </c>
       <c r="O10">
-        <v>1.506432866666666</v>
+        <v>1.497341141666666</v>
       </c>
       <c r="P10">
-        <v>10.54503006666667</v>
+        <v>10.48138799166667</v>
       </c>
       <c r="Q10">
-        <v>22.44503006666667</v>
+        <v>22.38138799166666</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1071037622519278</v>
+        <v>0.107699175638213</v>
       </c>
       <c r="T10">
-        <v>1.03366950187706</v>
+        <v>1.043709026953566</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.71159305119032</v>
+        <v>19.29919382328028</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1019673748307739</v>
+        <v>0.1018782883897741</v>
       </c>
       <c r="C11">
-        <v>142.9670614819116</v>
+        <v>141.6478174531443</v>
       </c>
       <c r="D11">
-        <v>155.1870614819116</v>
+        <v>155.3138174531443</v>
       </c>
       <c r="E11">
-        <v>-127.886</v>
+        <v>-126.44</v>
       </c>
       <c r="F11">
-        <v>13.014</v>
+        <v>14.46</v>
       </c>
       <c r="G11">
         <v>0.794</v>
@@ -2177,28 +2177,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M11">
-        <v>0.6546042</v>
+        <v>0.7273379999999999</v>
       </c>
       <c r="N11">
-        <v>11.97872913333333</v>
+        <v>11.90599533333333</v>
       </c>
       <c r="O11">
-        <v>1.497341141666666</v>
+        <v>1.488249416666666</v>
       </c>
       <c r="P11">
-        <v>10.48138799166667</v>
+        <v>10.41774591666666</v>
       </c>
       <c r="Q11">
-        <v>22.38138799166666</v>
+        <v>22.31774591666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.107699175638213</v>
+        <v>0.1083078204330824</v>
       </c>
       <c r="T11">
-        <v>1.043709026953566</v>
+        <v>1.053971652587328</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.29919382328028</v>
+        <v>17.36927444095226</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1018782883897741</v>
+        <v>0.1017892019487744</v>
       </c>
       <c r="C12">
-        <v>141.6478174531443</v>
+        <v>140.3287806608609</v>
       </c>
       <c r="D12">
-        <v>155.3138174531443</v>
+        <v>155.4407806608609</v>
       </c>
       <c r="E12">
-        <v>-126.44</v>
+        <v>-124.994</v>
       </c>
       <c r="F12">
-        <v>14.46</v>
+        <v>15.906</v>
       </c>
       <c r="G12">
         <v>0.794</v>
@@ -2259,28 +2259,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M12">
-        <v>0.727338</v>
+        <v>0.8000717999999999</v>
       </c>
       <c r="N12">
-        <v>11.90599533333333</v>
+        <v>11.83326153333333</v>
       </c>
       <c r="O12">
-        <v>1.488249416666666</v>
+        <v>1.479157691666666</v>
       </c>
       <c r="P12">
-        <v>10.41774591666666</v>
+        <v>10.35410384166667</v>
       </c>
       <c r="Q12">
-        <v>22.31774591666667</v>
+        <v>22.25410384166667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1083078204330824</v>
+        <v>0.1089301426390724</v>
       </c>
       <c r="T12">
-        <v>1.053971652587328</v>
+        <v>1.064464899021848</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.36927444095225</v>
+        <v>15.79024949177478</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1017892019487744</v>
+        <v>0.1017001155077747</v>
       </c>
       <c r="C13">
-        <v>140.3287806608609</v>
+        <v>139.0099516137011</v>
       </c>
       <c r="D13">
-        <v>155.4407806608609</v>
+        <v>155.5679516137011</v>
       </c>
       <c r="E13">
-        <v>-124.994</v>
+        <v>-123.548</v>
       </c>
       <c r="F13">
-        <v>15.906</v>
+        <v>17.352</v>
       </c>
       <c r="G13">
         <v>0.794</v>
@@ -2341,28 +2341,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M13">
-        <v>0.8000717999999999</v>
+        <v>0.8728056</v>
       </c>
       <c r="N13">
-        <v>11.83326153333333</v>
+        <v>11.76052773333333</v>
       </c>
       <c r="O13">
-        <v>1.479157691666666</v>
+        <v>1.470065966666666</v>
       </c>
       <c r="P13">
-        <v>10.35410384166667</v>
+        <v>10.29046176666666</v>
       </c>
       <c r="Q13">
-        <v>22.25410384166667</v>
+        <v>22.19046176666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1089301426390724</v>
+        <v>0.1095666085315622</v>
       </c>
       <c r="T13">
-        <v>1.064464899021848</v>
+        <v>1.07519662832988</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.79024949177478</v>
+        <v>14.47439536746021</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1017001155077747</v>
+        <v>0.101611029066775</v>
       </c>
       <c r="C14">
-        <v>139.0099516137011</v>
+        <v>137.6913308219708</v>
       </c>
       <c r="D14">
-        <v>155.5679516137011</v>
+        <v>155.6953308219708</v>
       </c>
       <c r="E14">
-        <v>-123.548</v>
+        <v>-122.102</v>
       </c>
       <c r="F14">
-        <v>17.352</v>
+        <v>18.798</v>
       </c>
       <c r="G14">
         <v>0.794</v>
@@ -2423,28 +2423,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M14">
-        <v>0.8728056</v>
+        <v>0.9455393999999999</v>
       </c>
       <c r="N14">
-        <v>11.76052773333333</v>
+        <v>11.68779393333333</v>
       </c>
       <c r="O14">
-        <v>1.470065966666666</v>
+        <v>1.460974241666666</v>
       </c>
       <c r="P14">
-        <v>10.29046176666666</v>
+        <v>10.22681969166667</v>
       </c>
       <c r="Q14">
-        <v>22.19046176666667</v>
+        <v>22.12681969166667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1095666085315622</v>
+        <v>0.1102177058238793</v>
       </c>
       <c r="T14">
-        <v>1.07519662832988</v>
+        <v>1.086175064058787</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.47439536746021</v>
+        <v>13.36098033919404</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.101611029066775</v>
+        <v>0.1017056926257753</v>
       </c>
       <c r="C15">
-        <v>137.6913308219708</v>
+        <v>136.1099841687596</v>
       </c>
       <c r="D15">
-        <v>155.6953308219708</v>
+        <v>155.5599841687595</v>
       </c>
       <c r="E15">
-        <v>-122.102</v>
+        <v>-120.656</v>
       </c>
       <c r="F15">
-        <v>18.798</v>
+        <v>20.244</v>
       </c>
       <c r="G15">
         <v>0.794</v>
@@ -2505,45 +2505,45 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M15">
-        <v>0.9455393999999999</v>
+        <v>1.0486392</v>
       </c>
       <c r="N15">
-        <v>11.68779393333333</v>
+        <v>11.58469413333333</v>
       </c>
       <c r="O15">
-        <v>1.460974241666666</v>
+        <v>1.448086766666666</v>
       </c>
       <c r="P15">
-        <v>10.22681969166667</v>
+        <v>10.13660736666666</v>
       </c>
       <c r="Q15">
-        <v>22.12681969166667</v>
+        <v>22.03660736666667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1102177058238793</v>
+        <v>0.1108839449136922</v>
       </c>
       <c r="T15">
-        <v>1.086175064058787</v>
+        <v>1.097408812246505</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.0440125</v>
+        <v>0.045325</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.36098033919404</v>
+        <v>12.04735940954079</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1017056926257753</v>
+        <v>0.1016297311847756</v>
       </c>
       <c r="C16">
-        <v>136.1099841687596</v>
+        <v>134.7725725207441</v>
       </c>
       <c r="D16">
-        <v>155.5599841687595</v>
+        <v>155.668572520744</v>
       </c>
       <c r="E16">
-        <v>-120.656</v>
+        <v>-119.21</v>
       </c>
       <c r="F16">
-        <v>20.244</v>
+        <v>21.69</v>
       </c>
       <c r="G16">
         <v>0.794</v>
@@ -2587,28 +2587,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M16">
-        <v>1.0486392</v>
+        <v>1.123542</v>
       </c>
       <c r="N16">
-        <v>11.58469413333333</v>
+        <v>11.50979133333333</v>
       </c>
       <c r="O16">
-        <v>1.448086766666666</v>
+        <v>1.438723916666666</v>
       </c>
       <c r="P16">
-        <v>10.13660736666666</v>
+        <v>10.07106741666666</v>
       </c>
       <c r="Q16">
-        <v>22.03660736666667</v>
+        <v>21.97106741666666</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1108839449136922</v>
+        <v>0.111565860217383</v>
       </c>
       <c r="T16">
-        <v>1.097408812246505</v>
+        <v>1.108906883920993</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.04735940954079</v>
+        <v>11.24420211557141</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1016297311847756</v>
+        <v>0.1015537697437759</v>
       </c>
       <c r="C17">
-        <v>134.7725725207441</v>
+        <v>133.4353125784128</v>
       </c>
       <c r="D17">
-        <v>155.6685725207441</v>
+        <v>155.7773125784128</v>
       </c>
       <c r="E17">
-        <v>-119.21</v>
+        <v>-117.764</v>
       </c>
       <c r="F17">
-        <v>21.69</v>
+        <v>23.136</v>
       </c>
       <c r="G17">
         <v>0.794</v>
@@ -2669,28 +2669,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M17">
-        <v>1.123542</v>
+        <v>1.1984448</v>
       </c>
       <c r="N17">
-        <v>11.50979133333333</v>
+        <v>11.43488853333333</v>
       </c>
       <c r="O17">
-        <v>1.438723916666666</v>
+        <v>1.429361066666667</v>
       </c>
       <c r="P17">
-        <v>10.07106741666666</v>
+        <v>10.00552746666667</v>
       </c>
       <c r="Q17">
-        <v>21.97106741666666</v>
+        <v>21.90552746666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.111565860217383</v>
+        <v>0.1122640115997332</v>
       </c>
       <c r="T17">
-        <v>1.108906883920993</v>
+        <v>1.120678719206779</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.24420211557141</v>
+        <v>10.5414394833482</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1015537697437759</v>
+        <v>0.1014778083027761</v>
       </c>
       <c r="C18">
-        <v>133.4353125784128</v>
+        <v>132.0982046599036</v>
       </c>
       <c r="D18">
-        <v>155.7773125784128</v>
+        <v>155.8862046599036</v>
       </c>
       <c r="E18">
-        <v>-117.764</v>
+        <v>-116.318</v>
       </c>
       <c r="F18">
-        <v>23.136</v>
+        <v>24.582</v>
       </c>
       <c r="G18">
         <v>0.794</v>
@@ -2751,28 +2751,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M18">
-        <v>1.1984448</v>
+        <v>1.2733476</v>
       </c>
       <c r="N18">
-        <v>11.43488853333333</v>
+        <v>11.35998573333333</v>
       </c>
       <c r="O18">
-        <v>1.429361066666667</v>
+        <v>1.419998216666666</v>
       </c>
       <c r="P18">
-        <v>10.00552746666667</v>
+        <v>9.939987516666665</v>
       </c>
       <c r="Q18">
-        <v>21.90552746666667</v>
+        <v>21.83998751666667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1122640115997332</v>
+        <v>0.1129789859069592</v>
       </c>
       <c r="T18">
-        <v>1.120678719206779</v>
+        <v>1.132734213174149</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.5414394833482</v>
+        <v>9.921354807857126</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1014778083027761</v>
+        <v>0.1016695968617764</v>
       </c>
       <c r="C19">
-        <v>132.0982046599036</v>
+        <v>130.377564866529</v>
       </c>
       <c r="D19">
-        <v>155.8862046599036</v>
+        <v>155.611564866529</v>
       </c>
       <c r="E19">
-        <v>-116.318</v>
+        <v>-114.872</v>
       </c>
       <c r="F19">
-        <v>24.582</v>
+        <v>26.028</v>
       </c>
       <c r="G19">
         <v>0.794</v>
@@ -2833,45 +2833,45 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M19">
-        <v>1.2733476</v>
+        <v>1.392498</v>
       </c>
       <c r="N19">
-        <v>11.35998573333333</v>
+        <v>11.24083533333333</v>
       </c>
       <c r="O19">
-        <v>1.419998216666666</v>
+        <v>1.405104416666666</v>
       </c>
       <c r="P19">
-        <v>9.939987516666665</v>
+        <v>9.835730916666664</v>
       </c>
       <c r="Q19">
-        <v>21.83998751666667</v>
+        <v>21.73573091666666</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1129789859069592</v>
+        <v>0.1137113986119225</v>
       </c>
       <c r="T19">
-        <v>1.132734213174149</v>
+        <v>1.145083743579749</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.045325</v>
+        <v>0.0468125</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.921354807857126</v>
+        <v>9.072424759915872</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1016695968617764</v>
+        <v>0.1016085104207767</v>
       </c>
       <c r="C20">
-        <v>130.377564866529</v>
+        <v>129.0189351107146</v>
       </c>
       <c r="D20">
-        <v>155.6115648665289</v>
+        <v>155.6989351107146</v>
       </c>
       <c r="E20">
-        <v>-114.872</v>
+        <v>-113.426</v>
       </c>
       <c r="F20">
-        <v>26.028</v>
+        <v>27.474</v>
       </c>
       <c r="G20">
         <v>0.794</v>
@@ -2915,28 +2915,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M20">
-        <v>1.392498</v>
+        <v>1.469859</v>
       </c>
       <c r="N20">
-        <v>11.24083533333333</v>
+        <v>11.16347433333333</v>
       </c>
       <c r="O20">
-        <v>1.405104416666666</v>
+        <v>1.395434291666666</v>
       </c>
       <c r="P20">
-        <v>9.835730916666664</v>
+        <v>9.768040041666666</v>
       </c>
       <c r="Q20">
-        <v>21.73573091666666</v>
+        <v>21.66804004166666</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1137113986119225</v>
+        <v>0.1144618955812058</v>
       </c>
       <c r="T20">
-        <v>1.145083743579749</v>
+        <v>1.157738200662029</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.072424759915872</v>
+        <v>8.594928719920301</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1016085104207767</v>
+        <v>0.101547423979777</v>
       </c>
       <c r="C21">
-        <v>129.0189351107146</v>
+        <v>127.6604035204568</v>
       </c>
       <c r="D21">
-        <v>155.6989351107146</v>
+        <v>155.7864035204568</v>
       </c>
       <c r="E21">
-        <v>-113.426</v>
+        <v>-111.98</v>
       </c>
       <c r="F21">
-        <v>27.474</v>
+        <v>28.92</v>
       </c>
       <c r="G21">
         <v>0.794</v>
@@ -2997,28 +2997,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M21">
-        <v>1.469859</v>
+        <v>1.54722</v>
       </c>
       <c r="N21">
-        <v>11.16347433333333</v>
+        <v>11.08611333333333</v>
       </c>
       <c r="O21">
-        <v>1.395434291666666</v>
+        <v>1.385764166666666</v>
       </c>
       <c r="P21">
-        <v>9.768040041666666</v>
+        <v>9.700349166666665</v>
       </c>
       <c r="Q21">
-        <v>21.66804004166666</v>
+        <v>21.60034916666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1144618955812058</v>
+        <v>0.1152311549747213</v>
       </c>
       <c r="T21">
-        <v>1.157738200662029</v>
+        <v>1.170709019171367</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.594928719920301</v>
+        <v>8.165182283924285</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.101547423979777</v>
+        <v>0.1014863375387773</v>
       </c>
       <c r="C22">
-        <v>127.6604035204568</v>
+        <v>126.3019702612907</v>
       </c>
       <c r="D22">
-        <v>155.7864035204568</v>
+        <v>155.8739702612907</v>
       </c>
       <c r="E22">
-        <v>-111.98</v>
+        <v>-110.534</v>
       </c>
       <c r="F22">
-        <v>28.92</v>
+        <v>30.366</v>
       </c>
       <c r="G22">
         <v>0.794</v>
@@ -3079,28 +3079,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M22">
-        <v>1.54722</v>
+        <v>1.624581</v>
       </c>
       <c r="N22">
-        <v>11.08611333333333</v>
+        <v>11.00875233333333</v>
       </c>
       <c r="O22">
-        <v>1.385764166666666</v>
+        <v>1.376094041666666</v>
       </c>
       <c r="P22">
-        <v>9.700349166666665</v>
+        <v>9.632658291666663</v>
       </c>
       <c r="Q22">
-        <v>21.60034916666667</v>
+        <v>21.53265829166666</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1152311549747213</v>
+        <v>0.1160198892895915</v>
       </c>
       <c r="T22">
-        <v>1.170709019171367</v>
+        <v>1.18400821283284</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.165182283924285</v>
+        <v>7.776364079927889</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1014863375387773</v>
+        <v>0.1015792510977776</v>
       </c>
       <c r="C23">
-        <v>126.3019702612907</v>
+        <v>124.7228186701577</v>
       </c>
       <c r="D23">
-        <v>155.8739702612907</v>
+        <v>155.7408186701577</v>
       </c>
       <c r="E23">
-        <v>-110.534</v>
+        <v>-109.088</v>
       </c>
       <c r="F23">
-        <v>30.366</v>
+        <v>31.812</v>
       </c>
       <c r="G23">
         <v>0.794</v>
@@ -3161,45 +3161,45 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M23">
-        <v>1.624581</v>
+        <v>1.7273916</v>
       </c>
       <c r="N23">
-        <v>11.00875233333333</v>
+        <v>10.90594173333333</v>
       </c>
       <c r="O23">
-        <v>1.376094041666666</v>
+        <v>1.363242716666667</v>
       </c>
       <c r="P23">
-        <v>9.632658291666665</v>
+        <v>9.542699016666665</v>
       </c>
       <c r="Q23">
-        <v>21.53265829166666</v>
+        <v>21.44269901666667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1160198892895915</v>
+        <v>0.1168288475612533</v>
       </c>
       <c r="T23">
-        <v>1.18400821283284</v>
+        <v>1.197648411459991</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.0468125</v>
+        <v>0.0475125</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.776364079927891</v>
+        <v>7.313531762764931</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1015792510977776</v>
+        <v>0.1015251646567778</v>
       </c>
       <c r="C24">
-        <v>124.7228186701577</v>
+        <v>123.354300619016</v>
       </c>
       <c r="D24">
-        <v>155.7408186701577</v>
+        <v>155.818300619016</v>
       </c>
       <c r="E24">
-        <v>-109.088</v>
+        <v>-107.642</v>
       </c>
       <c r="F24">
-        <v>31.812</v>
+        <v>33.258</v>
       </c>
       <c r="G24">
         <v>0.794</v>
@@ -3243,28 +3243,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M24">
-        <v>1.7273916</v>
+        <v>1.8059094</v>
       </c>
       <c r="N24">
-        <v>10.90594173333333</v>
+        <v>10.82742393333333</v>
       </c>
       <c r="O24">
-        <v>1.363242716666667</v>
+        <v>1.353427991666666</v>
       </c>
       <c r="P24">
-        <v>9.542699016666665</v>
+        <v>9.473995941666663</v>
       </c>
       <c r="Q24">
-        <v>21.44269901666667</v>
+        <v>21.37399594166666</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1168288475612533</v>
+        <v>0.1176588177360751</v>
       </c>
       <c r="T24">
-        <v>1.197648411459991</v>
+        <v>1.211642900960576</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.313531762764931</v>
+        <v>6.995552120905583</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1015251646567778</v>
+        <v>0.1014710782157781</v>
       </c>
       <c r="C25">
-        <v>123.354300619016</v>
+        <v>121.985859701675</v>
       </c>
       <c r="D25">
-        <v>155.818300619016</v>
+        <v>155.895859701675</v>
       </c>
       <c r="E25">
-        <v>-107.642</v>
+        <v>-106.196</v>
       </c>
       <c r="F25">
-        <v>33.258</v>
+        <v>34.704</v>
       </c>
       <c r="G25">
         <v>0.794</v>
@@ -3325,28 +3325,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M25">
-        <v>1.8059094</v>
+        <v>1.8844272</v>
       </c>
       <c r="N25">
-        <v>10.82742393333333</v>
+        <v>10.74890613333333</v>
       </c>
       <c r="O25">
-        <v>1.353427991666666</v>
+        <v>1.343613266666666</v>
       </c>
       <c r="P25">
-        <v>9.473995941666663</v>
+        <v>9.405292866666665</v>
       </c>
       <c r="Q25">
-        <v>21.37399594166666</v>
+        <v>21.30529286666667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1176588177360751</v>
+        <v>0.118510629231287</v>
       </c>
       <c r="T25">
-        <v>1.211642900960576</v>
+        <v>1.226005666500649</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.995552120905583</v>
+        <v>6.704070782534519</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1014710782157781</v>
+        <v>0.1014169917747784</v>
       </c>
       <c r="C26">
-        <v>121.985859701675</v>
+        <v>120.617496033373</v>
       </c>
       <c r="D26">
-        <v>155.895859701675</v>
+        <v>155.973496033373</v>
       </c>
       <c r="E26">
-        <v>-106.196</v>
+        <v>-104.75</v>
       </c>
       <c r="F26">
-        <v>34.704</v>
+        <v>36.15</v>
       </c>
       <c r="G26">
         <v>0.794</v>
@@ -3407,28 +3407,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M26">
-        <v>1.8844272</v>
+        <v>1.962945</v>
       </c>
       <c r="N26">
-        <v>10.74890613333333</v>
+        <v>10.67038833333333</v>
       </c>
       <c r="O26">
-        <v>1.343613266666666</v>
+        <v>1.333798541666666</v>
       </c>
       <c r="P26">
-        <v>9.405292866666665</v>
+        <v>9.336589791666665</v>
       </c>
       <c r="Q26">
-        <v>21.30529286666667</v>
+        <v>21.23658979166667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.118510629231287</v>
+        <v>0.1193851556997046</v>
       </c>
       <c r="T26">
-        <v>1.226005666500649</v>
+        <v>1.240751439121791</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.704070782534519</v>
+        <v>6.435907951233138</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1014169917747784</v>
+        <v>0.1013629053337787</v>
       </c>
       <c r="C27">
-        <v>120.617496033373</v>
+        <v>119.2492097295778</v>
       </c>
       <c r="D27">
-        <v>155.973496033373</v>
+        <v>156.0512097295777</v>
       </c>
       <c r="E27">
-        <v>-104.75</v>
+        <v>-103.304</v>
       </c>
       <c r="F27">
-        <v>36.15</v>
+        <v>37.596</v>
       </c>
       <c r="G27">
         <v>0.794</v>
@@ -3489,28 +3489,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M27">
-        <v>1.962945</v>
+        <v>2.0414628</v>
       </c>
       <c r="N27">
-        <v>10.67038833333333</v>
+        <v>10.59187053333333</v>
       </c>
       <c r="O27">
-        <v>1.333798541666666</v>
+        <v>1.323983816666666</v>
       </c>
       <c r="P27">
-        <v>9.336589791666665</v>
+        <v>9.267886716666665</v>
       </c>
       <c r="Q27">
-        <v>21.23658979166667</v>
+        <v>21.16788671666666</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1193851556997046</v>
+        <v>0.1202833180186199</v>
       </c>
       <c r="T27">
-        <v>1.240751439121791</v>
+        <v>1.255895746138099</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.435907951233138</v>
+        <v>6.188373030031864</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1013629053337787</v>
+        <v>0.101545068892779</v>
       </c>
       <c r="C28">
-        <v>119.2492097295778</v>
+        <v>117.5417776882654</v>
       </c>
       <c r="D28">
-        <v>156.0512097295777</v>
+        <v>155.7897776882654</v>
       </c>
       <c r="E28">
-        <v>-103.304</v>
+        <v>-101.858</v>
       </c>
       <c r="F28">
-        <v>37.596</v>
+        <v>39.042</v>
       </c>
       <c r="G28">
         <v>0.794</v>
@@ -3571,45 +3571,45 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M28">
-        <v>2.0414628</v>
+        <v>2.1590226</v>
       </c>
       <c r="N28">
-        <v>10.59187053333333</v>
+        <v>10.47431073333333</v>
       </c>
       <c r="O28">
-        <v>1.323983816666666</v>
+        <v>1.309288841666666</v>
       </c>
       <c r="P28">
-        <v>9.267886716666665</v>
+        <v>9.165021891666665</v>
       </c>
       <c r="Q28">
-        <v>21.16788671666666</v>
+        <v>21.06502189166667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1202833180186199</v>
+        <v>0.1212060875243548</v>
       </c>
       <c r="T28">
-        <v>1.255895746138099</v>
+        <v>1.271454965675401</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.0475125</v>
+        <v>0.0483875</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.188373030031864</v>
+        <v>5.851413196570212</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.101545068892779</v>
+        <v>0.1014997324517793</v>
       </c>
       <c r="C29">
-        <v>117.5417776882654</v>
+        <v>116.1607603756042</v>
       </c>
       <c r="D29">
-        <v>155.7897776882654</v>
+        <v>155.8547603756042</v>
       </c>
       <c r="E29">
-        <v>-101.858</v>
+        <v>-100.412</v>
       </c>
       <c r="F29">
-        <v>39.042</v>
+        <v>40.488</v>
       </c>
       <c r="G29">
         <v>0.794</v>
@@ -3653,28 +3653,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M29">
-        <v>2.1590226</v>
+        <v>2.2389864</v>
       </c>
       <c r="N29">
-        <v>10.47431073333333</v>
+        <v>10.39434693333333</v>
       </c>
       <c r="O29">
-        <v>1.309288841666666</v>
+        <v>1.299293366666666</v>
       </c>
       <c r="P29">
-        <v>9.165021891666665</v>
+        <v>9.095053566666664</v>
       </c>
       <c r="Q29">
-        <v>21.06502189166667</v>
+        <v>20.99505356666666</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1212060875243548</v>
+        <v>0.1221544895163601</v>
       </c>
       <c r="T29">
-        <v>1.271454965675401</v>
+        <v>1.287446385755407</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.851413196570212</v>
+        <v>5.642434153835562</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1014997324517793</v>
+        <v>0.1014543960107796</v>
       </c>
       <c r="C30">
-        <v>116.1607603756042</v>
+        <v>114.7797972964343</v>
       </c>
       <c r="D30">
-        <v>155.8547603756042</v>
+        <v>155.9197972964343</v>
       </c>
       <c r="E30">
-        <v>-100.412</v>
+        <v>-98.96600000000001</v>
       </c>
       <c r="F30">
-        <v>40.488</v>
+        <v>41.934</v>
       </c>
       <c r="G30">
         <v>0.794</v>
@@ -3735,28 +3735,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M30">
-        <v>2.2389864</v>
+        <v>2.3189502</v>
       </c>
       <c r="N30">
-        <v>10.39434693333333</v>
+        <v>10.31438313333333</v>
       </c>
       <c r="O30">
-        <v>1.299293366666666</v>
+        <v>1.289297891666666</v>
       </c>
       <c r="P30">
-        <v>9.095053566666664</v>
+        <v>9.025085241666664</v>
       </c>
       <c r="Q30">
-        <v>20.99505356666666</v>
+        <v>20.92508524166666</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1221544895163601</v>
+        <v>0.123129607057436</v>
       </c>
       <c r="T30">
-        <v>1.287446385755407</v>
+        <v>1.303888268372877</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.642434153835562</v>
+        <v>5.447867458875715</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1014543960107796</v>
+        <v>0.1014090595697798</v>
       </c>
       <c r="C31">
-        <v>114.7797972964343</v>
+        <v>113.3988885186776</v>
       </c>
       <c r="D31">
-        <v>155.9197972964343</v>
+        <v>155.9848885186776</v>
       </c>
       <c r="E31">
-        <v>-98.96600000000001</v>
+        <v>-97.52000000000001</v>
       </c>
       <c r="F31">
-        <v>41.934</v>
+        <v>43.38</v>
       </c>
       <c r="G31">
         <v>0.794</v>
@@ -3817,28 +3817,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M31">
-        <v>2.3189502</v>
+        <v>2.398914</v>
       </c>
       <c r="N31">
-        <v>10.31438313333333</v>
+        <v>10.23441933333333</v>
       </c>
       <c r="O31">
-        <v>1.289297891666666</v>
+        <v>1.279302416666666</v>
       </c>
       <c r="P31">
-        <v>9.025085241666664</v>
+        <v>8.955116916666665</v>
       </c>
       <c r="Q31">
-        <v>20.92508524166666</v>
+        <v>20.85511691666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.123129607057436</v>
+        <v>0.1241325850996855</v>
       </c>
       <c r="T31">
-        <v>1.303888268372877</v>
+        <v>1.320799919065132</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.447867458875716</v>
+        <v>5.266271876913192</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1014090595697798</v>
+        <v>0.1013637231287801</v>
       </c>
       <c r="C32">
-        <v>113.3988885186776</v>
+        <v>112.0180341103694</v>
       </c>
       <c r="D32">
-        <v>155.9848885186776</v>
+        <v>156.0500341103694</v>
       </c>
       <c r="E32">
-        <v>-97.52000000000001</v>
+        <v>-96.07400000000001</v>
       </c>
       <c r="F32">
-        <v>43.38</v>
+        <v>44.826</v>
       </c>
       <c r="G32">
         <v>0.794</v>
@@ -3899,28 +3899,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M32">
-        <v>2.398914</v>
+        <v>2.4788778</v>
       </c>
       <c r="N32">
-        <v>10.23441933333333</v>
+        <v>10.15445553333333</v>
       </c>
       <c r="O32">
-        <v>1.279302416666666</v>
+        <v>1.269306941666666</v>
       </c>
       <c r="P32">
-        <v>8.955116916666665</v>
+        <v>8.885148591666663</v>
       </c>
       <c r="Q32">
-        <v>20.85511691666667</v>
+        <v>20.78514859166666</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1241325850996855</v>
+        <v>0.1251646349692466</v>
       </c>
       <c r="T32">
-        <v>1.320799919065132</v>
+        <v>1.338201762531076</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.266271876913192</v>
+        <v>5.096392138948248</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1013637231287801</v>
+        <v>0.1013183866877804</v>
       </c>
       <c r="C33">
-        <v>112.0180341103694</v>
+        <v>110.6372341396589</v>
       </c>
       <c r="D33">
-        <v>156.0500341103694</v>
+        <v>156.1152341396589</v>
       </c>
       <c r="E33">
-        <v>-96.07400000000001</v>
+        <v>-94.62800000000001</v>
       </c>
       <c r="F33">
-        <v>44.826</v>
+        <v>46.272</v>
       </c>
       <c r="G33">
         <v>0.794</v>
@@ -3981,28 +3981,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M33">
-        <v>2.4788778</v>
+        <v>2.5588416</v>
       </c>
       <c r="N33">
-        <v>10.15445553333333</v>
+        <v>10.07449173333333</v>
       </c>
       <c r="O33">
-        <v>1.269306941666666</v>
+        <v>1.259311466666666</v>
       </c>
       <c r="P33">
-        <v>8.885148591666663</v>
+        <v>8.815180266666665</v>
       </c>
       <c r="Q33">
-        <v>20.78514859166666</v>
+        <v>20.71518026666666</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1251646349692466</v>
+        <v>0.1262270392467359</v>
       </c>
       <c r="T33">
-        <v>1.338201762531076</v>
+        <v>1.356115424922489</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.096392138948248</v>
+        <v>4.937129884606117</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1013183866877804</v>
+        <v>0.1012730502467807</v>
       </c>
       <c r="C34">
-        <v>110.6372341396589</v>
+        <v>109.2564886748091</v>
       </c>
       <c r="D34">
-        <v>156.1152341396589</v>
+        <v>156.1804886748091</v>
       </c>
       <c r="E34">
-        <v>-94.62800000000001</v>
+        <v>-93.182</v>
       </c>
       <c r="F34">
-        <v>46.272</v>
+        <v>47.718</v>
       </c>
       <c r="G34">
         <v>0.794</v>
@@ -4063,28 +4063,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M34">
-        <v>2.5588416</v>
+        <v>2.6388054</v>
       </c>
       <c r="N34">
-        <v>10.07449173333333</v>
+        <v>9.99452793333333</v>
       </c>
       <c r="O34">
-        <v>1.259311466666666</v>
+        <v>1.249315991666666</v>
       </c>
       <c r="P34">
-        <v>8.815180266666665</v>
+        <v>8.745211941666664</v>
       </c>
       <c r="Q34">
-        <v>20.71518026666666</v>
+        <v>20.64521194166667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1262270392467359</v>
+        <v>0.1273211570847473</v>
       </c>
       <c r="T34">
-        <v>1.356115424922489</v>
+        <v>1.37456382350469</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.937129884606117</v>
+        <v>4.7875198881029</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1012730502467807</v>
+        <v>0.101227713805781</v>
       </c>
       <c r="C35">
-        <v>109.2564886748091</v>
+        <v>107.8757977841972</v>
       </c>
       <c r="D35">
-        <v>156.1804886748091</v>
+        <v>156.2457977841972</v>
       </c>
       <c r="E35">
-        <v>-93.182</v>
+        <v>-91.736</v>
       </c>
       <c r="F35">
-        <v>47.718</v>
+        <v>49.164</v>
       </c>
       <c r="G35">
         <v>0.794</v>
@@ -4145,28 +4145,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M35">
-        <v>2.6388054</v>
+        <v>2.7187692</v>
       </c>
       <c r="N35">
-        <v>9.99452793333333</v>
+        <v>9.914564133333331</v>
       </c>
       <c r="O35">
-        <v>1.249315991666666</v>
+        <v>1.239320516666666</v>
       </c>
       <c r="P35">
-        <v>8.745211941666664</v>
+        <v>8.675243616666664</v>
       </c>
       <c r="Q35">
-        <v>20.64521194166667</v>
+        <v>20.57524361666666</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1273211570847473</v>
+        <v>0.1284484300087591</v>
       </c>
       <c r="T35">
-        <v>1.37456382350469</v>
+        <v>1.39357126446817</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.7875198881029</v>
+        <v>4.646710479629286</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.101227713805781</v>
+        <v>0.1011823773647813</v>
       </c>
       <c r="C36">
-        <v>107.8757977841972</v>
+        <v>106.4951615363149</v>
       </c>
       <c r="D36">
-        <v>156.2457977841972</v>
+        <v>156.3111615363149</v>
       </c>
       <c r="E36">
-        <v>-91.736</v>
+        <v>-90.29000000000001</v>
       </c>
       <c r="F36">
-        <v>49.164</v>
+        <v>50.61</v>
       </c>
       <c r="G36">
         <v>0.794</v>
@@ -4227,28 +4227,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M36">
-        <v>2.7187692</v>
+        <v>2.798733</v>
       </c>
       <c r="N36">
-        <v>9.914564133333331</v>
+        <v>9.834600333333331</v>
       </c>
       <c r="O36">
-        <v>1.239320516666666</v>
+        <v>1.229325041666666</v>
       </c>
       <c r="P36">
-        <v>8.675243616666664</v>
+        <v>8.605275291666665</v>
       </c>
       <c r="Q36">
-        <v>20.57524361666666</v>
+        <v>20.50527529166666</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1284484300087591</v>
+        <v>0.1296103882535097</v>
       </c>
       <c r="T36">
-        <v>1.39357126446817</v>
+        <v>1.413163549768988</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.646710479629286</v>
+        <v>4.51394732306845</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1011823773647813</v>
+        <v>0.1019245409237816</v>
       </c>
       <c r="C37">
-        <v>106.4951615363149</v>
+        <v>103.9859815493542</v>
       </c>
       <c r="D37">
-        <v>156.3111615363149</v>
+        <v>155.2479815493542</v>
       </c>
       <c r="E37">
-        <v>-90.29000000000001</v>
+        <v>-88.84399999999999</v>
       </c>
       <c r="F37">
-        <v>50.61</v>
+        <v>52.056</v>
       </c>
       <c r="G37">
         <v>0.794</v>
@@ -4309,45 +4309,45 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M37">
-        <v>2.798733</v>
+        <v>3.008836800000001</v>
       </c>
       <c r="N37">
-        <v>9.834600333333331</v>
+        <v>9.62449653333333</v>
       </c>
       <c r="O37">
-        <v>1.229325041666666</v>
+        <v>1.203062066666666</v>
       </c>
       <c r="P37">
-        <v>8.605275291666665</v>
+        <v>8.421434466666664</v>
       </c>
       <c r="Q37">
-        <v>20.50527529166666</v>
+        <v>20.32143446666667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1296103882535097</v>
+        <v>0.1308086576934087</v>
       </c>
       <c r="T37">
-        <v>1.413163549768988</v>
+        <v>1.433368093985456</v>
       </c>
       <c r="U37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.0483875</v>
+        <v>0.050575</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.51394732306845</v>
+        <v>4.198743292867638</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1019245409237816</v>
+        <v>0.1019010794827819</v>
       </c>
       <c r="C38">
-        <v>103.9859815493542</v>
+        <v>102.5733696114324</v>
       </c>
       <c r="D38">
-        <v>155.2479815493542</v>
+        <v>155.2813696114324</v>
       </c>
       <c r="E38">
-        <v>-88.84400000000001</v>
+        <v>-87.39800000000001</v>
       </c>
       <c r="F38">
-        <v>52.056</v>
+        <v>53.502</v>
       </c>
       <c r="G38">
         <v>0.794</v>
@@ -4391,28 +4391,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M38">
-        <v>3.0088368</v>
+        <v>3.0924156</v>
       </c>
       <c r="N38">
-        <v>9.624496533333332</v>
+        <v>9.54091773333333</v>
       </c>
       <c r="O38">
-        <v>1.203062066666666</v>
+        <v>1.192614716666666</v>
       </c>
       <c r="P38">
-        <v>8.421434466666666</v>
+        <v>8.348303016666664</v>
       </c>
       <c r="Q38">
-        <v>20.32143446666667</v>
+        <v>20.24830301666666</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1308086576934087</v>
+        <v>0.1320449674329871</v>
       </c>
       <c r="T38">
-        <v>1.433368093985456</v>
+        <v>1.454214052304034</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.19874329286764</v>
+        <v>4.085263744411757</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1019010794827819</v>
+        <v>0.1030413680417821</v>
       </c>
       <c r="C39">
-        <v>102.5733696114324</v>
+        <v>99.52106195022333</v>
       </c>
       <c r="D39">
-        <v>155.2813696114324</v>
+        <v>153.6750619502233</v>
       </c>
       <c r="E39">
-        <v>-87.39800000000001</v>
+        <v>-85.952</v>
       </c>
       <c r="F39">
-        <v>53.502</v>
+        <v>54.948</v>
       </c>
       <c r="G39">
         <v>0.794</v>
@@ -4473,45 +4473,45 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M39">
-        <v>3.0924156</v>
+        <v>3.3683124</v>
       </c>
       <c r="N39">
-        <v>9.54091773333333</v>
+        <v>9.26502093333333</v>
       </c>
       <c r="O39">
-        <v>1.192614716666666</v>
+        <v>1.158127616666666</v>
       </c>
       <c r="P39">
-        <v>8.348303016666664</v>
+        <v>8.106893316666664</v>
       </c>
       <c r="Q39">
-        <v>20.24830301666666</v>
+        <v>20.00689331666666</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1320449674329871</v>
+        <v>0.1333211581319067</v>
       </c>
       <c r="T39">
-        <v>1.454214052304034</v>
+        <v>1.475732460890954</v>
       </c>
       <c r="U39">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0.125</v>
       </c>
       <c r="W39">
-        <v>0.050575</v>
+        <v>0.0536375</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.085263744411757</v>
+        <v>3.750641814973377</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1030413680417821</v>
+        <v>0.1030485316007824</v>
       </c>
       <c r="C40">
-        <v>99.52106195022333</v>
+        <v>98.06507578775373</v>
       </c>
       <c r="D40">
-        <v>153.6750619502233</v>
+        <v>153.6650757877537</v>
       </c>
       <c r="E40">
-        <v>-85.952</v>
+        <v>-84.506</v>
       </c>
       <c r="F40">
-        <v>54.948</v>
+        <v>56.394</v>
       </c>
       <c r="G40">
         <v>0.794</v>
@@ -4555,28 +4555,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M40">
-        <v>3.3683124</v>
+        <v>3.4569522</v>
       </c>
       <c r="N40">
-        <v>9.26502093333333</v>
+        <v>9.176381133333331</v>
       </c>
       <c r="O40">
-        <v>1.158127616666666</v>
+        <v>1.147047641666666</v>
       </c>
       <c r="P40">
-        <v>8.106893316666664</v>
+        <v>8.029333491666664</v>
       </c>
       <c r="Q40">
-        <v>20.00689331666666</v>
+        <v>19.92933349166666</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1333211581319067</v>
+        <v>0.1346391911488236</v>
       </c>
       <c r="T40">
-        <v>1.475732460890954</v>
+        <v>1.497956391070887</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.750641814973377</v>
+        <v>3.654471512025342</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1030485316007824</v>
+        <v>0.1030556951597827</v>
       </c>
       <c r="C41">
-        <v>98.06507578775373</v>
+        <v>96.60909092304783</v>
       </c>
       <c r="D41">
-        <v>153.6650757877537</v>
+        <v>153.6550909230478</v>
       </c>
       <c r="E41">
-        <v>-84.506</v>
+        <v>-83.06</v>
       </c>
       <c r="F41">
-        <v>56.394</v>
+        <v>57.84</v>
       </c>
       <c r="G41">
         <v>0.794</v>
@@ -4637,28 +4637,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M41">
-        <v>3.4569522</v>
+        <v>3.545592</v>
       </c>
       <c r="N41">
-        <v>9.176381133333331</v>
+        <v>9.08774133333333</v>
       </c>
       <c r="O41">
-        <v>1.147047641666666</v>
+        <v>1.135967666666666</v>
       </c>
       <c r="P41">
-        <v>8.029333491666664</v>
+        <v>7.951773666666664</v>
       </c>
       <c r="Q41">
-        <v>19.92933349166666</v>
+        <v>19.85177366666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1346391911488236</v>
+        <v>0.1360011585996379</v>
       </c>
       <c r="T41">
-        <v>1.497956391070887</v>
+        <v>1.520921118923485</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.654471512025342</v>
+        <v>3.563109724224708</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1030556951597827</v>
+        <v>0.104067358718783</v>
       </c>
       <c r="C42">
-        <v>96.60909092304783</v>
+        <v>93.76590524553274</v>
       </c>
       <c r="D42">
-        <v>153.6550909230478</v>
+        <v>152.2579052455327</v>
       </c>
       <c r="E42">
-        <v>-83.06</v>
+        <v>-81.614</v>
       </c>
       <c r="F42">
-        <v>57.84</v>
+        <v>59.286</v>
       </c>
       <c r="G42">
         <v>0.794</v>
@@ -4719,45 +4719,45 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M42">
-        <v>3.545592</v>
+        <v>3.8002326</v>
       </c>
       <c r="N42">
-        <v>9.08774133333333</v>
+        <v>8.833100733333332</v>
       </c>
       <c r="O42">
-        <v>1.135967666666666</v>
+        <v>1.104137591666666</v>
       </c>
       <c r="P42">
-        <v>7.951773666666664</v>
+        <v>7.728963141666665</v>
       </c>
       <c r="Q42">
-        <v>19.85177366666667</v>
+        <v>19.62896314166667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1360011585996379</v>
+        <v>0.1374092944386153</v>
       </c>
       <c r="T42">
-        <v>1.520921118923485</v>
+        <v>1.544664312127019</v>
       </c>
       <c r="U42">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.0536375</v>
+        <v>0.05608750000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.563109724224708</v>
+        <v>3.32435791781096</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.104067358718783</v>
+        <v>0.1040990222777833</v>
       </c>
       <c r="C43">
-        <v>93.76590524553274</v>
+        <v>92.27658538380416</v>
       </c>
       <c r="D43">
-        <v>152.2579052455327</v>
+        <v>152.2145853838041</v>
       </c>
       <c r="E43">
-        <v>-81.614</v>
+        <v>-80.16800000000001</v>
       </c>
       <c r="F43">
-        <v>59.286</v>
+        <v>60.73200000000001</v>
       </c>
       <c r="G43">
         <v>0.794</v>
@@ -4801,28 +4801,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M43">
-        <v>3.8002326</v>
+        <v>3.892921200000001</v>
       </c>
       <c r="N43">
-        <v>8.833100733333332</v>
+        <v>8.740412133333329</v>
       </c>
       <c r="O43">
-        <v>1.104137591666666</v>
+        <v>1.092551516666666</v>
       </c>
       <c r="P43">
-        <v>7.728963141666665</v>
+        <v>7.647860616666663</v>
       </c>
       <c r="Q43">
-        <v>19.62896314166667</v>
+        <v>19.54786061666666</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1374092944386153</v>
+        <v>0.1388659866858333</v>
       </c>
       <c r="T43">
-        <v>1.544664312127019</v>
+        <v>1.569226236130674</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.32435791781096</v>
+        <v>3.24520653881546</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1040990222777833</v>
+        <v>0.1041306858367836</v>
       </c>
       <c r="C44">
-        <v>92.27658538380416</v>
+        <v>90.78729016548098</v>
       </c>
       <c r="D44">
-        <v>152.2145853838041</v>
+        <v>152.171290165481</v>
       </c>
       <c r="E44">
-        <v>-80.16800000000001</v>
+        <v>-78.72200000000001</v>
       </c>
       <c r="F44">
-        <v>60.73199999999999</v>
+        <v>62.178</v>
       </c>
       <c r="G44">
         <v>0.794</v>
@@ -4883,28 +4883,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M44">
-        <v>3.8929212</v>
+        <v>3.9856098</v>
       </c>
       <c r="N44">
-        <v>8.740412133333331</v>
+        <v>8.64772353333333</v>
       </c>
       <c r="O44">
-        <v>1.092551516666666</v>
+        <v>1.080965441666666</v>
       </c>
       <c r="P44">
-        <v>7.647860616666665</v>
+        <v>7.566758091666664</v>
       </c>
       <c r="Q44">
-        <v>19.54786061666666</v>
+        <v>19.46675809166666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1388659866858332</v>
+        <v>0.1403737909417256</v>
       </c>
       <c r="T44">
-        <v>1.569226236130674</v>
+        <v>1.594649982029194</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.245206538815461</v>
+        <v>3.169736619308124</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1041306858367836</v>
+        <v>0.1041623493957839</v>
       </c>
       <c r="C45">
-        <v>90.78729016548098</v>
+        <v>89.29801956954091</v>
       </c>
       <c r="D45">
-        <v>152.171290165481</v>
+        <v>152.1280195695409</v>
       </c>
       <c r="E45">
-        <v>-78.72200000000001</v>
+        <v>-77.27600000000001</v>
       </c>
       <c r="F45">
-        <v>62.178</v>
+        <v>63.624</v>
       </c>
       <c r="G45">
         <v>0.794</v>
@@ -4965,28 +4965,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M45">
-        <v>3.9856098</v>
+        <v>4.0782984</v>
       </c>
       <c r="N45">
-        <v>8.64772353333333</v>
+        <v>8.555034933333332</v>
       </c>
       <c r="O45">
-        <v>1.080965441666666</v>
+        <v>1.069379366666666</v>
       </c>
       <c r="P45">
-        <v>7.566758091666664</v>
+        <v>7.485655566666665</v>
       </c>
       <c r="Q45">
-        <v>19.46675809166666</v>
+        <v>19.38565556666666</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1403737909417256</v>
+        <v>0.141935445349614</v>
       </c>
       <c r="T45">
-        <v>1.594649982029194</v>
+        <v>1.620981718852662</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.169736619308124</v>
+        <v>3.097697150687486</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1041623493957839</v>
+        <v>0.1041940129547841</v>
       </c>
       <c r="C46">
-        <v>89.29801956954091</v>
+        <v>87.80877357498539</v>
       </c>
       <c r="D46">
-        <v>152.1280195695409</v>
+        <v>152.0847735749854</v>
       </c>
       <c r="E46">
-        <v>-77.27600000000001</v>
+        <v>-75.83000000000001</v>
       </c>
       <c r="F46">
-        <v>63.624</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="G46">
         <v>0.794</v>
@@ -5047,28 +5047,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M46">
-        <v>4.0782984</v>
+        <v>4.170987</v>
       </c>
       <c r="N46">
-        <v>8.555034933333332</v>
+        <v>8.462346333333331</v>
       </c>
       <c r="O46">
-        <v>1.069379366666666</v>
+        <v>1.057793291666666</v>
       </c>
       <c r="P46">
-        <v>7.485655566666665</v>
+        <v>7.404553041666665</v>
       </c>
       <c r="Q46">
-        <v>19.38565556666666</v>
+        <v>19.30455304166667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.141935445349614</v>
+        <v>0.1435538871905166</v>
       </c>
       <c r="T46">
-        <v>1.620981718852662</v>
+        <v>1.648270973378801</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.097697150687486</v>
+        <v>3.028859436227763</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1041940129547841</v>
+        <v>0.1073651765137844</v>
       </c>
       <c r="C47">
-        <v>87.80877357498539</v>
+        <v>82.15270204831502</v>
       </c>
       <c r="D47">
-        <v>152.0847735749854</v>
+        <v>147.874702048315</v>
       </c>
       <c r="E47">
-        <v>-75.83000000000001</v>
+        <v>-74.384</v>
       </c>
       <c r="F47">
-        <v>65.06999999999999</v>
+        <v>66.51600000000001</v>
       </c>
       <c r="G47">
         <v>0.794</v>
@@ -5129,45 +5129,45 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M47">
-        <v>4.170987</v>
+        <v>4.782500400000001</v>
       </c>
       <c r="N47">
-        <v>8.462346333333331</v>
+        <v>7.85083293333333</v>
       </c>
       <c r="O47">
-        <v>1.057793291666666</v>
+        <v>0.9813541166666663</v>
       </c>
       <c r="P47">
-        <v>7.404553041666665</v>
+        <v>6.869478816666664</v>
       </c>
       <c r="Q47">
-        <v>19.30455304166667</v>
+        <v>18.76947881666666</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1435538871905166</v>
+        <v>0.145232271321823</v>
       </c>
       <c r="T47">
-        <v>1.648270973378801</v>
+        <v>1.676570941035538</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.125</v>
       </c>
       <c r="W47">
-        <v>0.05608750000000001</v>
+        <v>0.06291250000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.028859436227763</v>
+        <v>2.641574966378117</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1073651765137844</v>
+        <v>0.1074650900727847</v>
       </c>
       <c r="C48">
-        <v>82.15270204831502</v>
+        <v>80.57784007206295</v>
       </c>
       <c r="D48">
-        <v>147.874702048315</v>
+        <v>147.7458400720629</v>
       </c>
       <c r="E48">
-        <v>-74.384</v>
+        <v>-72.938</v>
       </c>
       <c r="F48">
-        <v>66.51600000000001</v>
+        <v>67.962</v>
       </c>
       <c r="G48">
         <v>0.794</v>
@@ -5211,28 +5211,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M48">
-        <v>4.782500400000001</v>
+        <v>4.886467800000001</v>
       </c>
       <c r="N48">
-        <v>7.85083293333333</v>
+        <v>7.74686553333333</v>
       </c>
       <c r="O48">
-        <v>0.9813541166666663</v>
+        <v>0.9683581916666663</v>
       </c>
       <c r="P48">
-        <v>6.869478816666664</v>
+        <v>6.778507341666664</v>
       </c>
       <c r="Q48">
-        <v>18.76947881666666</v>
+        <v>18.67850734166667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.145232271321823</v>
+        <v>0.1469739907033674</v>
       </c>
       <c r="T48">
-        <v>1.676570941035538</v>
+        <v>1.705938832000076</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.641574966378117</v>
+        <v>2.58537124368922</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1074650900727847</v>
+        <v>0.107565003631785</v>
       </c>
       <c r="C49">
-        <v>80.57784007206295</v>
+        <v>79.00320248782513</v>
       </c>
       <c r="D49">
-        <v>147.7458400720629</v>
+        <v>147.6172024878251</v>
       </c>
       <c r="E49">
-        <v>-72.938</v>
+        <v>-71.492</v>
       </c>
       <c r="F49">
-        <v>67.962</v>
+        <v>69.408</v>
       </c>
       <c r="G49">
         <v>0.794</v>
@@ -5293,28 +5293,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M49">
-        <v>4.886467800000001</v>
+        <v>4.9904352</v>
       </c>
       <c r="N49">
-        <v>7.74686553333333</v>
+        <v>7.642898133333331</v>
       </c>
       <c r="O49">
-        <v>0.9683581916666663</v>
+        <v>0.9553622666666663</v>
       </c>
       <c r="P49">
-        <v>6.778507341666664</v>
+        <v>6.687535866666664</v>
       </c>
       <c r="Q49">
-        <v>18.67850734166667</v>
+        <v>18.58753586666666</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1469739907033674</v>
+        <v>0.1487826992918942</v>
       </c>
       <c r="T49">
-        <v>1.705938832000076</v>
+        <v>1.736436257232481</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.58537124368922</v>
+        <v>2.531509342779029</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.107565003631785</v>
+        <v>0.1093370421907853</v>
       </c>
       <c r="C50">
-        <v>79.00320248782516</v>
+        <v>75.31237364317901</v>
       </c>
       <c r="D50">
-        <v>147.6172024878252</v>
+        <v>145.372373643179</v>
       </c>
       <c r="E50">
-        <v>-71.492</v>
+        <v>-70.04600000000001</v>
       </c>
       <c r="F50">
-        <v>69.408</v>
+        <v>70.854</v>
       </c>
       <c r="G50">
         <v>0.794</v>
@@ -5375,45 +5375,45 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M50">
-        <v>4.9904352</v>
+        <v>5.3707332</v>
       </c>
       <c r="N50">
-        <v>7.642898133333331</v>
+        <v>7.262600133333331</v>
       </c>
       <c r="O50">
-        <v>0.9553622666666663</v>
+        <v>0.9078250166666664</v>
       </c>
       <c r="P50">
-        <v>6.687535866666664</v>
+        <v>6.354775116666665</v>
       </c>
       <c r="Q50">
-        <v>18.58753586666666</v>
+        <v>18.25477511666666</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1487826992918942</v>
+        <v>0.1506623376289908</v>
       </c>
       <c r="T50">
-        <v>1.736436257232481</v>
+        <v>1.768129659924981</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.125</v>
       </c>
       <c r="W50">
-        <v>0.06291250000000001</v>
+        <v>0.06632500000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.531509342779029</v>
+        <v>2.352254871519838</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1093370421907853</v>
+        <v>0.1094710807497856</v>
       </c>
       <c r="C51">
-        <v>75.31237364317901</v>
+        <v>73.699347114497</v>
       </c>
       <c r="D51">
-        <v>145.372373643179</v>
+        <v>145.205347114497</v>
       </c>
       <c r="E51">
-        <v>-70.04600000000001</v>
+        <v>-68.60000000000001</v>
       </c>
       <c r="F51">
-        <v>70.854</v>
+        <v>72.3</v>
       </c>
       <c r="G51">
         <v>0.794</v>
@@ -5457,28 +5457,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M51">
-        <v>5.3707332</v>
+        <v>5.48034</v>
       </c>
       <c r="N51">
-        <v>7.262600133333331</v>
+        <v>7.152993333333331</v>
       </c>
       <c r="O51">
-        <v>0.9078250166666664</v>
+        <v>0.8941241666666664</v>
       </c>
       <c r="P51">
-        <v>6.354775116666665</v>
+        <v>6.258869166666665</v>
       </c>
       <c r="Q51">
-        <v>18.25477511666666</v>
+        <v>18.15886916666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1506623376289908</v>
+        <v>0.1526171614995711</v>
       </c>
       <c r="T51">
-        <v>1.768129659924981</v>
+        <v>1.80109079872518</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.352254871519838</v>
+        <v>2.305209774089442</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1094710807497856</v>
+        <v>0.1096051193087859</v>
       </c>
       <c r="C52">
-        <v>73.699347114497</v>
+        <v>72.08670395775754</v>
       </c>
       <c r="D52">
-        <v>145.205347114497</v>
+        <v>145.0387039577575</v>
       </c>
       <c r="E52">
-        <v>-68.60000000000001</v>
+        <v>-67.15400000000001</v>
       </c>
       <c r="F52">
-        <v>72.3</v>
+        <v>73.746</v>
       </c>
       <c r="G52">
         <v>0.794</v>
@@ -5539,28 +5539,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M52">
-        <v>5.48034</v>
+        <v>5.5899468</v>
       </c>
       <c r="N52">
-        <v>7.152993333333331</v>
+        <v>7.043386533333331</v>
       </c>
       <c r="O52">
-        <v>0.8941241666666664</v>
+        <v>0.8804233166666664</v>
       </c>
       <c r="P52">
-        <v>6.258869166666665</v>
+        <v>6.162963216666665</v>
       </c>
       <c r="Q52">
-        <v>18.15886916666667</v>
+        <v>18.06296321666667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1526171614995711</v>
+        <v>0.154651774099563</v>
       </c>
       <c r="T52">
-        <v>1.80109079872518</v>
+        <v>1.835397290129469</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.305209774089442</v>
+        <v>2.260009582440629</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1096051193087859</v>
+        <v>0.1097391578677862</v>
       </c>
       <c r="C53">
-        <v>72.08670395775754</v>
+        <v>70.47444285455721</v>
       </c>
       <c r="D53">
-        <v>145.0387039577575</v>
+        <v>144.8724428545572</v>
       </c>
       <c r="E53">
-        <v>-67.15400000000001</v>
+        <v>-65.70800000000001</v>
       </c>
       <c r="F53">
-        <v>73.746</v>
+        <v>75.19199999999999</v>
       </c>
       <c r="G53">
         <v>0.794</v>
@@ -5621,28 +5621,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M53">
-        <v>5.5899468</v>
+        <v>5.6995536</v>
       </c>
       <c r="N53">
-        <v>7.043386533333331</v>
+        <v>6.933779733333331</v>
       </c>
       <c r="O53">
-        <v>0.8804233166666664</v>
+        <v>0.8667224666666664</v>
       </c>
       <c r="P53">
-        <v>6.162963216666665</v>
+        <v>6.067057266666665</v>
       </c>
       <c r="Q53">
-        <v>18.06296321666667</v>
+        <v>17.96705726666666</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.154651774099563</v>
+        <v>0.1567711622245545</v>
       </c>
       <c r="T53">
-        <v>1.835397290129469</v>
+        <v>1.871133218675604</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.260009582440629</v>
+        <v>2.216547859701386</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1097391578677862</v>
+        <v>0.1098731964267864</v>
       </c>
       <c r="C54">
-        <v>70.47444285455721</v>
+        <v>68.86256249253094</v>
       </c>
       <c r="D54">
-        <v>144.8724428545572</v>
+        <v>144.7065624925309</v>
       </c>
       <c r="E54">
-        <v>-65.70800000000001</v>
+        <v>-64.262</v>
       </c>
       <c r="F54">
-        <v>75.19199999999999</v>
+        <v>76.63800000000001</v>
       </c>
       <c r="G54">
         <v>0.794</v>
@@ -5703,28 +5703,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M54">
-        <v>5.6995536</v>
+        <v>5.809160400000001</v>
       </c>
       <c r="N54">
-        <v>6.933779733333331</v>
+        <v>6.824172933333331</v>
       </c>
       <c r="O54">
-        <v>0.8667224666666664</v>
+        <v>0.8530216166666663</v>
       </c>
       <c r="P54">
-        <v>6.067057266666665</v>
+        <v>5.971151316666664</v>
       </c>
       <c r="Q54">
-        <v>17.96705726666666</v>
+        <v>17.87115131666667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1567711622245545</v>
+        <v>0.158980737078269</v>
       </c>
       <c r="T54">
-        <v>1.871133218675604</v>
+        <v>1.908389825032212</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.216547859701386</v>
+        <v>2.174726201971171</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1098731964267864</v>
+        <v>0.1100072349857867</v>
       </c>
       <c r="C55">
-        <v>68.86256249253094</v>
+        <v>67.2510615653174</v>
       </c>
       <c r="D55">
-        <v>144.7065624925309</v>
+        <v>144.5410615653174</v>
       </c>
       <c r="E55">
-        <v>-64.262</v>
+        <v>-62.816</v>
       </c>
       <c r="F55">
-        <v>76.63800000000001</v>
+        <v>78.084</v>
       </c>
       <c r="G55">
         <v>0.794</v>
@@ -5785,28 +5785,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M55">
-        <v>5.809160400000001</v>
+        <v>5.9187672</v>
       </c>
       <c r="N55">
-        <v>6.824172933333331</v>
+        <v>6.714566133333331</v>
       </c>
       <c r="O55">
-        <v>0.8530216166666663</v>
+        <v>0.8393207666666663</v>
       </c>
       <c r="P55">
-        <v>5.971151316666664</v>
+        <v>5.875245366666665</v>
       </c>
       <c r="Q55">
-        <v>17.87115131666667</v>
+        <v>17.77524536666667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.158980737078269</v>
+        <v>0.1612863804038842</v>
       </c>
       <c r="T55">
-        <v>1.908389825032212</v>
+        <v>1.947266283839108</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.174726201971171</v>
+        <v>2.134453494527261</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1100072349857867</v>
+        <v>0.110141273544787</v>
       </c>
       <c r="C56">
-        <v>67.2510615653174</v>
+        <v>65.63993877252491</v>
       </c>
       <c r="D56">
-        <v>144.5410615653174</v>
+        <v>144.3759387725249</v>
       </c>
       <c r="E56">
-        <v>-62.816</v>
+        <v>-61.37</v>
       </c>
       <c r="F56">
-        <v>78.084</v>
+        <v>79.53</v>
       </c>
       <c r="G56">
         <v>0.794</v>
@@ -5867,28 +5867,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M56">
-        <v>5.9187672</v>
+        <v>6.028374</v>
       </c>
       <c r="N56">
-        <v>6.714566133333331</v>
+        <v>6.604959333333331</v>
       </c>
       <c r="O56">
-        <v>0.8393207666666663</v>
+        <v>0.8256199166666663</v>
       </c>
       <c r="P56">
-        <v>5.875245366666665</v>
+        <v>5.779339416666664</v>
       </c>
       <c r="Q56">
-        <v>17.77524536666667</v>
+        <v>17.67933941666666</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1612863804038842</v>
+        <v>0.1636944967661934</v>
       </c>
       <c r="T56">
-        <v>1.947266283839108</v>
+        <v>1.987870585259643</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.134453494527261</v>
+        <v>2.09564524917222</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.110141273544787</v>
+        <v>0.1102753121037873</v>
       </c>
       <c r="C57">
-        <v>65.63993877252491</v>
+        <v>64.02919281969704</v>
       </c>
       <c r="D57">
-        <v>144.3759387725249</v>
+        <v>144.211192819697</v>
       </c>
       <c r="E57">
-        <v>-61.37</v>
+        <v>-59.92400000000001</v>
       </c>
       <c r="F57">
-        <v>79.53</v>
+        <v>80.976</v>
       </c>
       <c r="G57">
         <v>0.794</v>
@@ -5949,28 +5949,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M57">
-        <v>6.028374</v>
+        <v>6.1379808</v>
       </c>
       <c r="N57">
-        <v>6.604959333333331</v>
+        <v>6.495352533333331</v>
       </c>
       <c r="O57">
-        <v>0.8256199166666663</v>
+        <v>0.8119190666666664</v>
       </c>
       <c r="P57">
-        <v>5.779339416666664</v>
+        <v>5.683433466666664</v>
       </c>
       <c r="Q57">
-        <v>17.67933941666666</v>
+        <v>17.58343346666667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1636944967661934</v>
+        <v>0.1662120729631529</v>
       </c>
       <c r="T57">
-        <v>1.987870585259643</v>
+        <v>2.030320536744749</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.09564524917222</v>
+        <v>2.058223012579859</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1102753121037873</v>
+        <v>0.1104093506627876</v>
       </c>
       <c r="C58">
-        <v>64.02919281969704</v>
+        <v>62.41882241827913</v>
       </c>
       <c r="D58">
-        <v>144.211192819697</v>
+        <v>144.0468224182791</v>
       </c>
       <c r="E58">
-        <v>-59.92400000000001</v>
+        <v>-58.47799999999999</v>
       </c>
       <c r="F58">
-        <v>80.976</v>
+        <v>82.42200000000001</v>
       </c>
       <c r="G58">
         <v>0.794</v>
@@ -6031,28 +6031,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M58">
-        <v>6.1379808</v>
+        <v>6.247587600000001</v>
       </c>
       <c r="N58">
-        <v>6.495352533333331</v>
+        <v>6.38574573333333</v>
       </c>
       <c r="O58">
-        <v>0.8119190666666664</v>
+        <v>0.7982182166666663</v>
       </c>
       <c r="P58">
-        <v>5.683433466666664</v>
+        <v>5.587527516666664</v>
       </c>
       <c r="Q58">
-        <v>17.58343346666667</v>
+        <v>17.48752751666666</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1662120729631529</v>
+        <v>0.168846745727413</v>
       </c>
       <c r="T58">
-        <v>2.030320536744749</v>
+        <v>2.074744904577998</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.058223012579859</v>
+        <v>2.022113836920563</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1104093506627876</v>
+        <v>0.1177498892217879</v>
       </c>
       <c r="C59">
-        <v>62.41882241827913</v>
+        <v>52.50970588420863</v>
       </c>
       <c r="D59">
-        <v>144.0468224182791</v>
+        <v>135.5837058842086</v>
       </c>
       <c r="E59">
-        <v>-58.47799999999999</v>
+        <v>-57.032</v>
       </c>
       <c r="F59">
-        <v>82.42200000000001</v>
+        <v>83.86800000000001</v>
       </c>
       <c r="G59">
         <v>0.794</v>
@@ -6113,45 +6113,45 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M59">
-        <v>6.247587600000001</v>
+        <v>7.548120000000001</v>
       </c>
       <c r="N59">
-        <v>6.38574573333333</v>
+        <v>5.08521333333333</v>
       </c>
       <c r="O59">
-        <v>0.7982182166666663</v>
+        <v>0.6356516666666663</v>
       </c>
       <c r="P59">
-        <v>5.587527516666664</v>
+        <v>4.449561666666664</v>
       </c>
       <c r="Q59">
-        <v>17.48752751666666</v>
+        <v>16.34956166666667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.168846745727413</v>
+        <v>0.171606879099495</v>
       </c>
       <c r="T59">
-        <v>2.074744904577998</v>
+        <v>2.121284718498546</v>
       </c>
       <c r="U59">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V59">
         <v>0.125</v>
       </c>
       <c r="W59">
-        <v>0.06632500000000001</v>
+        <v>0.07875</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.022113836920563</v>
+        <v>1.673705947087928</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1177498892217879</v>
+        <v>0.1180081777807881</v>
       </c>
       <c r="C60">
-        <v>52.50970588420867</v>
+        <v>50.7839916981105</v>
       </c>
       <c r="D60">
-        <v>135.5837058842087</v>
+        <v>135.3039916981105</v>
       </c>
       <c r="E60">
-        <v>-57.03200000000001</v>
+        <v>-55.58600000000001</v>
       </c>
       <c r="F60">
-        <v>83.86799999999999</v>
+        <v>85.31399999999999</v>
       </c>
       <c r="G60">
         <v>0.794</v>
@@ -6195,28 +6195,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M60">
-        <v>7.548119999999999</v>
+        <v>7.678259999999999</v>
       </c>
       <c r="N60">
-        <v>5.085213333333332</v>
+        <v>4.955073333333332</v>
       </c>
       <c r="O60">
-        <v>0.6356516666666665</v>
+        <v>0.6193841666666665</v>
       </c>
       <c r="P60">
-        <v>4.449561666666666</v>
+        <v>4.335689166666666</v>
       </c>
       <c r="Q60">
-        <v>16.34956166666667</v>
+        <v>16.23568916666667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1716068790994949</v>
+        <v>0.1745016531238735</v>
       </c>
       <c r="T60">
-        <v>2.121284718498545</v>
+        <v>2.170094767244485</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.673705947087928</v>
+        <v>1.645338049679658</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1180081777807881</v>
+        <v>0.1182664663397884</v>
       </c>
       <c r="C61">
-        <v>50.7839916981105</v>
+        <v>49.0594292572851</v>
       </c>
       <c r="D61">
-        <v>135.3039916981105</v>
+        <v>135.0254292572851</v>
       </c>
       <c r="E61">
-        <v>-55.58600000000001</v>
+        <v>-54.14000000000001</v>
       </c>
       <c r="F61">
-        <v>85.31399999999999</v>
+        <v>86.75999999999999</v>
       </c>
       <c r="G61">
         <v>0.794</v>
@@ -6277,28 +6277,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M61">
-        <v>7.678259999999999</v>
+        <v>7.808399999999999</v>
       </c>
       <c r="N61">
-        <v>4.955073333333332</v>
+        <v>4.824933333333332</v>
       </c>
       <c r="O61">
-        <v>0.6193841666666665</v>
+        <v>0.6031166666666665</v>
       </c>
       <c r="P61">
-        <v>4.335689166666666</v>
+        <v>4.221816666666665</v>
       </c>
       <c r="Q61">
-        <v>16.23568916666667</v>
+        <v>16.12181666666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1745016531238735</v>
+        <v>0.1775411658494711</v>
       </c>
       <c r="T61">
-        <v>2.170094767244485</v>
+        <v>2.221345318427722</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.645338049679658</v>
+        <v>1.617915748851664</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1182664663397884</v>
+        <v>0.1185247548987887</v>
       </c>
       <c r="C62">
-        <v>49.0594292572851</v>
+        <v>47.33601146274452</v>
       </c>
       <c r="D62">
-        <v>135.0254292572851</v>
+        <v>134.7480114627445</v>
       </c>
       <c r="E62">
-        <v>-54.14000000000001</v>
+        <v>-52.69400000000002</v>
       </c>
       <c r="F62">
-        <v>86.75999999999999</v>
+        <v>88.20599999999999</v>
       </c>
       <c r="G62">
         <v>0.794</v>
@@ -6359,28 +6359,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M62">
-        <v>7.808399999999999</v>
+        <v>7.938539999999999</v>
       </c>
       <c r="N62">
-        <v>4.824933333333332</v>
+        <v>4.694793333333332</v>
       </c>
       <c r="O62">
-        <v>0.6031166666666665</v>
+        <v>0.5868491666666665</v>
       </c>
       <c r="P62">
-        <v>4.221816666666665</v>
+        <v>4.107944166666666</v>
       </c>
       <c r="Q62">
-        <v>16.12181666666667</v>
+        <v>16.00794416666667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1775411658494711</v>
+        <v>0.1807365510225352</v>
       </c>
       <c r="T62">
-        <v>2.221345318427722</v>
+        <v>2.275224103004971</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.617915748851664</v>
+        <v>1.591392539854096</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1185247548987887</v>
+        <v>0.118783043457789</v>
       </c>
       <c r="C63">
-        <v>47.33601146274452</v>
+        <v>45.61373127372225</v>
       </c>
       <c r="D63">
-        <v>134.7480114627445</v>
+        <v>134.4717312737222</v>
       </c>
       <c r="E63">
-        <v>-52.69400000000002</v>
+        <v>-51.248</v>
       </c>
       <c r="F63">
-        <v>88.20599999999999</v>
+        <v>89.652</v>
       </c>
       <c r="G63">
         <v>0.794</v>
@@ -6441,28 +6441,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M63">
-        <v>7.938539999999999</v>
+        <v>8.068680000000001</v>
       </c>
       <c r="N63">
-        <v>4.694793333333332</v>
+        <v>4.564653333333331</v>
       </c>
       <c r="O63">
-        <v>0.5868491666666665</v>
+        <v>0.5705816666666663</v>
       </c>
       <c r="P63">
-        <v>4.107944166666666</v>
+        <v>3.994071666666664</v>
       </c>
       <c r="Q63">
-        <v>16.00794416666667</v>
+        <v>15.89407166666667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1807365510225352</v>
+        <v>0.1841001143626026</v>
       </c>
       <c r="T63">
-        <v>2.275224103004971</v>
+        <v>2.331938613086285</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.591392539854096</v>
+        <v>1.565724918243546</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.118783043457789</v>
+        <v>0.1190413320167893</v>
       </c>
       <c r="C64">
-        <v>45.61373127372225</v>
+        <v>43.89258170707784</v>
       </c>
       <c r="D64">
-        <v>134.4717312737222</v>
+        <v>134.1965817070778</v>
       </c>
       <c r="E64">
-        <v>-51.248</v>
+        <v>-49.80200000000001</v>
       </c>
       <c r="F64">
-        <v>89.652</v>
+        <v>91.098</v>
       </c>
       <c r="G64">
         <v>0.794</v>
@@ -6523,28 +6523,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M64">
-        <v>8.068680000000001</v>
+        <v>8.19882</v>
       </c>
       <c r="N64">
-        <v>4.564653333333331</v>
+        <v>4.434513333333332</v>
       </c>
       <c r="O64">
-        <v>0.5705816666666663</v>
+        <v>0.5543141666666664</v>
       </c>
       <c r="P64">
-        <v>3.994071666666664</v>
+        <v>3.880199166666665</v>
       </c>
       <c r="Q64">
-        <v>15.89407166666667</v>
+        <v>15.78019916666667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1841001143626026</v>
+        <v>0.1876454919372684</v>
       </c>
       <c r="T64">
-        <v>2.331938613086285</v>
+        <v>2.391718772361185</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.565724918243546</v>
+        <v>1.540872141763489</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1190413320167893</v>
+        <v>0.1192996205757896</v>
       </c>
       <c r="C65">
-        <v>43.89258170707784</v>
+        <v>42.17255583670833</v>
       </c>
       <c r="D65">
-        <v>134.1965817070778</v>
+        <v>133.9225558367083</v>
       </c>
       <c r="E65">
-        <v>-49.80200000000001</v>
+        <v>-48.35600000000001</v>
       </c>
       <c r="F65">
-        <v>91.098</v>
+        <v>92.544</v>
       </c>
       <c r="G65">
         <v>0.794</v>
@@ -6605,28 +6605,28 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M65">
-        <v>8.19882</v>
+        <v>8.328959999999999</v>
       </c>
       <c r="N65">
-        <v>4.434513333333332</v>
+        <v>4.304373333333332</v>
       </c>
       <c r="O65">
-        <v>0.5543141666666664</v>
+        <v>0.5380466666666666</v>
       </c>
       <c r="P65">
-        <v>3.880199166666665</v>
+        <v>3.766326666666666</v>
       </c>
       <c r="Q65">
-        <v>15.78019916666667</v>
+        <v>15.66632666666667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1876454919372684</v>
+        <v>0.1913878349327488</v>
       </c>
       <c r="T65">
-        <v>2.391718772361185</v>
+        <v>2.454820051595801</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.540872141763489</v>
+        <v>1.516796014548435</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1192996205757896</v>
+        <v>0.153260100212897</v>
       </c>
       <c r="C66">
-        <v>42.17255583670833</v>
+        <v>12.38084059937168</v>
       </c>
       <c r="D66">
-        <v>133.9225558367083</v>
+        <v>105.5768405993717</v>
       </c>
       <c r="E66">
-        <v>-48.35600000000001</v>
+        <v>-46.91000000000001</v>
       </c>
       <c r="F66">
-        <v>92.544</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="G66">
         <v>0.794</v>
@@ -6687,45 +6687,45 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M66">
-        <v>8.328959999999999</v>
+        <v>13.797732</v>
       </c>
       <c r="N66">
-        <v>4.304373333333332</v>
+        <v>-1.164398666666669</v>
       </c>
       <c r="O66">
-        <v>0.5380466666666666</v>
+        <v>-0.1455498333333336</v>
       </c>
       <c r="P66">
-        <v>3.766326666666666</v>
+        <v>-1.018848833333335</v>
       </c>
       <c r="Q66">
-        <v>15.66632666666667</v>
+        <v>10.88115116666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1913878349327488</v>
+        <v>0.1964600900504163</v>
       </c>
       <c r="T66">
-        <v>2.454820051595801</v>
+        <v>2.540345559790982</v>
       </c>
       <c r="U66">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.125</v>
+        <v>0.1144511769518836</v>
       </c>
       <c r="W66">
-        <v>0.07875</v>
+        <v>0.1299985672234635</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.516796014548435</v>
+        <v>0.9156094156150686</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.153260100212897</v>
+        <v>0.154270100212897</v>
       </c>
       <c r="C67">
-        <v>12.38084059937168</v>
+        <v>10.27441380221235</v>
       </c>
       <c r="D67">
-        <v>105.5768405993717</v>
+        <v>104.9164138022124</v>
       </c>
       <c r="E67">
-        <v>-46.91000000000001</v>
+        <v>-45.464</v>
       </c>
       <c r="F67">
-        <v>93.98999999999999</v>
+        <v>95.43600000000001</v>
       </c>
       <c r="G67">
         <v>0.794</v>
@@ -6769,37 +6769,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M67">
-        <v>13.797732</v>
+        <v>14.0100048</v>
       </c>
       <c r="N67">
-        <v>-1.164398666666669</v>
+        <v>-1.376671466666672</v>
       </c>
       <c r="O67">
-        <v>-0.1455498333333336</v>
+        <v>-0.1720839333333339</v>
       </c>
       <c r="P67">
-        <v>-1.018848833333335</v>
+        <v>-1.204587533333338</v>
       </c>
       <c r="Q67">
-        <v>10.88115116666667</v>
+        <v>10.69541246666666</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1964600900504163</v>
+        <v>0.2008912691695462</v>
       </c>
       <c r="T67">
-        <v>2.540345559790982</v>
+        <v>2.615061605667187</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1144511769518836</v>
+        <v>0.1127170682101883</v>
       </c>
       <c r="W67">
-        <v>0.1299985672234635</v>
+        <v>0.1302531343867444</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9156094156150686</v>
+        <v>0.9017365456815067</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.154270100212897</v>
+        <v>0.155280100212897</v>
       </c>
       <c r="C68">
-        <v>10.27441380221235</v>
+        <v>8.176198126537884</v>
       </c>
       <c r="D68">
-        <v>104.9164138022124</v>
+        <v>104.2641981265379</v>
       </c>
       <c r="E68">
-        <v>-45.464</v>
+        <v>-44.018</v>
       </c>
       <c r="F68">
-        <v>95.43600000000001</v>
+        <v>96.88200000000001</v>
       </c>
       <c r="G68">
         <v>0.794</v>
@@ -6851,37 +6851,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M68">
-        <v>14.0100048</v>
+        <v>14.2222776</v>
       </c>
       <c r="N68">
-        <v>-1.376671466666672</v>
+        <v>-1.588944266666671</v>
       </c>
       <c r="O68">
-        <v>-0.1720839333333339</v>
+        <v>-0.1986180333333338</v>
       </c>
       <c r="P68">
-        <v>-1.204587533333338</v>
+        <v>-1.390326233333337</v>
       </c>
       <c r="Q68">
-        <v>10.69541246666666</v>
+        <v>10.50967376666666</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2008912691695462</v>
+        <v>0.2055910045989264</v>
       </c>
       <c r="T68">
-        <v>2.615061605667187</v>
+        <v>2.694305896748012</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1127170682101883</v>
+        <v>0.1110347239085437</v>
       </c>
       <c r="W68">
-        <v>0.1302531343867444</v>
+        <v>0.1305001025302258</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9017365456815067</v>
+        <v>0.8882777912683499</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.155280100212897</v>
+        <v>0.156290100212897</v>
       </c>
       <c r="C69">
-        <v>8.176198126537884</v>
+        <v>6.086041384463257</v>
       </c>
       <c r="D69">
-        <v>104.2641981265379</v>
+        <v>103.6200413844633</v>
       </c>
       <c r="E69">
-        <v>-44.018</v>
+        <v>-42.572</v>
       </c>
       <c r="F69">
-        <v>96.88200000000001</v>
+        <v>98.328</v>
       </c>
       <c r="G69">
         <v>0.794</v>
@@ -6933,37 +6933,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M69">
-        <v>14.2222776</v>
+        <v>14.4345504</v>
       </c>
       <c r="N69">
-        <v>-1.588944266666671</v>
+        <v>-1.801217066666672</v>
       </c>
       <c r="O69">
-        <v>-0.1986180333333338</v>
+        <v>-0.2251521333333339</v>
       </c>
       <c r="P69">
-        <v>-1.390326233333337</v>
+        <v>-1.576064933333338</v>
       </c>
       <c r="Q69">
-        <v>10.50967376666666</v>
+        <v>10.32393506666666</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2055910045989264</v>
+        <v>0.2105844734926428</v>
       </c>
       <c r="T69">
-        <v>2.694305896748012</v>
+        <v>2.778502956021387</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1110347239085437</v>
+        <v>0.1094018603216534</v>
       </c>
       <c r="W69">
-        <v>0.1305001025302258</v>
+        <v>0.1307398069047813</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8882777912683499</v>
+        <v>0.8752148825732271</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.156290100212897</v>
+        <v>0.157300100212897</v>
       </c>
       <c r="C70">
-        <v>6.086041384463257</v>
+        <v>4.003795125950774</v>
       </c>
       <c r="D70">
-        <v>103.6200413844633</v>
+        <v>102.9837951259508</v>
       </c>
       <c r="E70">
-        <v>-42.572</v>
+        <v>-41.126</v>
       </c>
       <c r="F70">
-        <v>98.328</v>
+        <v>99.774</v>
       </c>
       <c r="G70">
         <v>0.794</v>
@@ -7015,37 +7015,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M70">
-        <v>14.4345504</v>
+        <v>14.6468232</v>
       </c>
       <c r="N70">
-        <v>-1.801217066666672</v>
+        <v>-2.013489866666671</v>
       </c>
       <c r="O70">
-        <v>-0.2251521333333339</v>
+        <v>-0.2516862333333338</v>
       </c>
       <c r="P70">
-        <v>-1.576064933333338</v>
+        <v>-1.761803633333337</v>
       </c>
       <c r="Q70">
-        <v>10.32393506666666</v>
+        <v>10.13819636666666</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2105844734926428</v>
+        <v>0.2159001016698249</v>
       </c>
       <c r="T70">
-        <v>2.778502956021387</v>
+        <v>2.86813208363498</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1094018603216534</v>
+        <v>0.1078163261140932</v>
       </c>
       <c r="W70">
-        <v>0.1307398069047813</v>
+        <v>0.1309725633264511</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8752148825732271</v>
+        <v>0.8625306089127456</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.157300100212897</v>
+        <v>0.158310100212897</v>
       </c>
       <c r="C71">
-        <v>4.003795125950774</v>
+        <v>1.929314524754972</v>
       </c>
       <c r="D71">
-        <v>102.9837951259508</v>
+        <v>102.355314524755</v>
       </c>
       <c r="E71">
-        <v>-41.126</v>
+        <v>-39.68000000000001</v>
       </c>
       <c r="F71">
-        <v>99.774</v>
+        <v>101.22</v>
       </c>
       <c r="G71">
         <v>0.794</v>
@@ -7097,37 +7097,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M71">
-        <v>14.6468232</v>
+        <v>14.859096</v>
       </c>
       <c r="N71">
-        <v>-2.013489866666671</v>
+        <v>-2.22576266666667</v>
       </c>
       <c r="O71">
-        <v>-0.2516862333333338</v>
+        <v>-0.2782203333333337</v>
       </c>
       <c r="P71">
-        <v>-1.761803633333337</v>
+        <v>-1.947542333333336</v>
       </c>
       <c r="Q71">
-        <v>10.13819636666666</v>
+        <v>9.952457666666664</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2159001016698249</v>
+        <v>0.221570105058819</v>
       </c>
       <c r="T71">
-        <v>2.86813208363498</v>
+        <v>2.963736486422813</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1078163261140932</v>
+        <v>0.1062760928838919</v>
       </c>
       <c r="W71">
-        <v>0.1309725633264511</v>
+        <v>0.1311986695646447</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8625306089127456</v>
+        <v>0.850208743071135</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.158310100212897</v>
+        <v>0.159320100212897</v>
       </c>
       <c r="C72">
-        <v>1.929314524754972</v>
+        <v>-0.1375417314815905</v>
       </c>
       <c r="D72">
-        <v>102.355314524755</v>
+        <v>101.7344582685184</v>
       </c>
       <c r="E72">
-        <v>-39.68000000000001</v>
+        <v>-38.23399999999999</v>
       </c>
       <c r="F72">
-        <v>101.22</v>
+        <v>102.666</v>
       </c>
       <c r="G72">
         <v>0.794</v>
@@ -7179,37 +7179,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M72">
-        <v>14.859096</v>
+        <v>15.0713688</v>
       </c>
       <c r="N72">
-        <v>-2.22576266666667</v>
+        <v>-2.438035466666673</v>
       </c>
       <c r="O72">
-        <v>-0.2782203333333337</v>
+        <v>-0.3047544333333341</v>
       </c>
       <c r="P72">
-        <v>-1.947542333333336</v>
+        <v>-2.133281033333339</v>
       </c>
       <c r="Q72">
-        <v>9.952457666666664</v>
+        <v>9.766718966666662</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.221570105058819</v>
+        <v>0.2276311431642956</v>
       </c>
       <c r="T72">
-        <v>2.963736486422813</v>
+        <v>3.065934296299462</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1062760928838919</v>
+        <v>0.1047792465052455</v>
       </c>
       <c r="W72">
-        <v>0.1311986695646447</v>
+        <v>0.13141840661303</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.850208743071135</v>
+        <v>0.8382339720419639</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.159320100212897</v>
+        <v>0.160330100212897</v>
       </c>
       <c r="C73">
-        <v>-0.1375417314815763</v>
+        <v>-2.196911547156461</v>
       </c>
       <c r="D73">
-        <v>101.7344582685184</v>
+        <v>101.1210884528435</v>
       </c>
       <c r="E73">
-        <v>-38.23400000000001</v>
+        <v>-36.78800000000001</v>
       </c>
       <c r="F73">
-        <v>102.666</v>
+        <v>104.112</v>
       </c>
       <c r="G73">
         <v>0.794</v>
@@ -7261,37 +7261,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M73">
-        <v>15.0713688</v>
+        <v>15.2836416</v>
       </c>
       <c r="N73">
-        <v>-2.438035466666669</v>
+        <v>-2.65030826666667</v>
       </c>
       <c r="O73">
-        <v>-0.3047544333333336</v>
+        <v>-0.3312885333333337</v>
       </c>
       <c r="P73">
-        <v>-2.133281033333335</v>
+        <v>-2.319019733333336</v>
       </c>
       <c r="Q73">
-        <v>9.766718966666666</v>
+        <v>9.580980266666664</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2276311431642955</v>
+        <v>0.2341251125630203</v>
       </c>
       <c r="T73">
-        <v>3.065934296299461</v>
+        <v>3.175431949738727</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1047792465052455</v>
+        <v>0.1033239791926727</v>
       </c>
       <c r="W73">
-        <v>0.13141840661303</v>
+        <v>0.1316320398545157</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8382339720419641</v>
+        <v>0.8265918335413813</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.160330100212897</v>
+        <v>0.161340100212897</v>
       </c>
       <c r="C74">
-        <v>-2.196911547156461</v>
+        <v>-4.248929520827033</v>
       </c>
       <c r="D74">
-        <v>101.1210884528435</v>
+        <v>100.515070479173</v>
       </c>
       <c r="E74">
-        <v>-36.78800000000001</v>
+        <v>-35.34200000000001</v>
       </c>
       <c r="F74">
-        <v>104.112</v>
+        <v>105.558</v>
       </c>
       <c r="G74">
         <v>0.794</v>
@@ -7343,37 +7343,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M74">
-        <v>15.2836416</v>
+        <v>15.4959144</v>
       </c>
       <c r="N74">
-        <v>-2.65030826666667</v>
+        <v>-2.862581066666669</v>
       </c>
       <c r="O74">
-        <v>-0.3312885333333337</v>
+        <v>-0.3578226333333336</v>
       </c>
       <c r="P74">
-        <v>-2.319019733333336</v>
+        <v>-2.504758433333335</v>
       </c>
       <c r="Q74">
-        <v>9.580980266666664</v>
+        <v>9.395241566666666</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2341251125630203</v>
+        <v>0.2411001167320211</v>
       </c>
       <c r="T74">
-        <v>3.175431949738727</v>
+        <v>3.293040540469791</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1033239791926727</v>
+        <v>0.1019085822174306</v>
       </c>
       <c r="W74">
-        <v>0.1316320398545157</v>
+        <v>0.1318398201304812</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8265918335413813</v>
+        <v>0.8152686577394446</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.161340100212897</v>
+        <v>0.162350100212897</v>
       </c>
       <c r="C75">
-        <v>-4.248929520827033</v>
+        <v>-6.293727043679468</v>
       </c>
       <c r="D75">
-        <v>100.515070479173</v>
+        <v>99.91627295632053</v>
       </c>
       <c r="E75">
-        <v>-35.34200000000001</v>
+        <v>-33.89600000000002</v>
       </c>
       <c r="F75">
-        <v>105.558</v>
+        <v>107.004</v>
       </c>
       <c r="G75">
         <v>0.794</v>
@@ -7425,37 +7425,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M75">
-        <v>15.4959144</v>
+        <v>15.7081872</v>
       </c>
       <c r="N75">
-        <v>-2.862581066666669</v>
+        <v>-3.074853866666668</v>
       </c>
       <c r="O75">
-        <v>-0.3578226333333336</v>
+        <v>-0.3843567333333335</v>
       </c>
       <c r="P75">
-        <v>-2.504758433333335</v>
+        <v>-2.690497133333335</v>
       </c>
       <c r="Q75">
-        <v>9.395241566666666</v>
+        <v>9.209502866666666</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2411001167320211</v>
+        <v>0.2486116596832527</v>
       </c>
       <c r="T75">
-        <v>3.293040540469791</v>
+        <v>3.419695945872475</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1019085822174306</v>
+        <v>0.1005314392144923</v>
       </c>
       <c r="W75">
-        <v>0.1318398201304812</v>
+        <v>0.1320419847233125</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8152686577394446</v>
+        <v>0.8042515137159386</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.162350100212897</v>
+        <v>0.2049998340238272</v>
       </c>
       <c r="C76">
-        <v>-6.293727043679468</v>
+        <v>-27.82269419824107</v>
       </c>
       <c r="D76">
-        <v>99.91627295632053</v>
+        <v>79.83330580175893</v>
       </c>
       <c r="E76">
-        <v>-33.89600000000002</v>
+        <v>-32.45000000000002</v>
       </c>
       <c r="F76">
-        <v>107.004</v>
+        <v>108.45</v>
       </c>
       <c r="G76">
         <v>0.794</v>
@@ -7507,45 +7507,45 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M76">
-        <v>15.7081872</v>
+        <v>21.77676</v>
       </c>
       <c r="N76">
-        <v>-3.074853866666668</v>
+        <v>-9.143426666666668</v>
       </c>
       <c r="O76">
-        <v>-0.3843567333333335</v>
+        <v>-1.142928333333334</v>
       </c>
       <c r="P76">
-        <v>-2.690497133333335</v>
+        <v>-8.000498333333335</v>
       </c>
       <c r="Q76">
-        <v>9.209502866666666</v>
+        <v>3.899501666666666</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2486116596832527</v>
+        <v>0.2612830613143035</v>
       </c>
       <c r="T76">
-        <v>3.419695945872475</v>
+        <v>3.633353981381391</v>
       </c>
       <c r="U76">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1005314392144923</v>
+        <v>0.07251614412183752</v>
       </c>
       <c r="W76">
-        <v>0.1320419847233125</v>
+        <v>0.186238758260335</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.8042515137159386</v>
+        <v>0.5801291529747001</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2049998340238272</v>
+        <v>0.2065498340238272</v>
       </c>
       <c r="C77">
-        <v>-27.82269419824107</v>
+        <v>-29.8476297830492</v>
       </c>
       <c r="D77">
-        <v>79.83330580175893</v>
+        <v>79.2543702169508</v>
       </c>
       <c r="E77">
-        <v>-32.45000000000002</v>
+        <v>-31.004</v>
       </c>
       <c r="F77">
-        <v>108.45</v>
+        <v>109.896</v>
       </c>
       <c r="G77">
         <v>0.794</v>
@@ -7589,37 +7589,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M77">
-        <v>21.77676</v>
+        <v>22.0671168</v>
       </c>
       <c r="N77">
-        <v>-9.143426666666668</v>
+        <v>-9.43378346666667</v>
       </c>
       <c r="O77">
-        <v>-1.142928333333334</v>
+        <v>-1.179222933333334</v>
       </c>
       <c r="P77">
-        <v>-8.000498333333335</v>
+        <v>-8.254560533333336</v>
       </c>
       <c r="Q77">
-        <v>3.899501666666666</v>
+        <v>3.645439466666664</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2612830613143035</v>
+        <v>0.2702615222023995</v>
       </c>
       <c r="T77">
-        <v>3.633353981381391</v>
+        <v>3.784743730605617</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.07251614412183752</v>
+        <v>0.07156198433076071</v>
       </c>
       <c r="W77">
-        <v>0.186238758260335</v>
+        <v>0.1864303535463833</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5801291529747001</v>
+        <v>0.5724958746460856</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2065498340238272</v>
+        <v>0.2080998340238271</v>
       </c>
       <c r="C78">
-        <v>-29.8476297830492</v>
+        <v>-31.86422916417544</v>
       </c>
       <c r="D78">
-        <v>79.2543702169508</v>
+        <v>78.68377083582456</v>
       </c>
       <c r="E78">
-        <v>-31.004</v>
+        <v>-29.55800000000001</v>
       </c>
       <c r="F78">
-        <v>109.896</v>
+        <v>111.342</v>
       </c>
       <c r="G78">
         <v>0.794</v>
@@ -7671,37 +7671,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M78">
-        <v>22.0671168</v>
+        <v>22.3574736</v>
       </c>
       <c r="N78">
-        <v>-9.43378346666667</v>
+        <v>-9.724140266666668</v>
       </c>
       <c r="O78">
-        <v>-1.179222933333334</v>
+        <v>-1.215517533333333</v>
       </c>
       <c r="P78">
-        <v>-8.254560533333336</v>
+        <v>-8.508622733333334</v>
       </c>
       <c r="Q78">
-        <v>3.645439466666664</v>
+        <v>3.391377266666666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2702615222023995</v>
+        <v>0.2800207188198952</v>
       </c>
       <c r="T78">
-        <v>3.784743730605617</v>
+        <v>3.949297805849339</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.07156198433076071</v>
+        <v>0.0706326079108807</v>
       </c>
       <c r="W78">
-        <v>0.1864303535463833</v>
+        <v>0.1866169723314952</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5724958746460856</v>
+        <v>0.5650608632870456</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2080998340238271</v>
+        <v>0.2096498340238271</v>
       </c>
       <c r="C79">
-        <v>-31.86422916417544</v>
+        <v>-33.87267110646064</v>
       </c>
       <c r="D79">
-        <v>78.68377083582456</v>
+        <v>78.12132889353936</v>
       </c>
       <c r="E79">
-        <v>-29.55800000000001</v>
+        <v>-28.11200000000001</v>
       </c>
       <c r="F79">
-        <v>111.342</v>
+        <v>112.788</v>
       </c>
       <c r="G79">
         <v>0.794</v>
@@ -7753,37 +7753,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M79">
-        <v>22.3574736</v>
+        <v>22.6478304</v>
       </c>
       <c r="N79">
-        <v>-9.724140266666668</v>
+        <v>-10.01449706666667</v>
       </c>
       <c r="O79">
-        <v>-1.215517533333333</v>
+        <v>-1.251812133333334</v>
       </c>
       <c r="P79">
-        <v>-8.508622733333334</v>
+        <v>-8.762684933333336</v>
       </c>
       <c r="Q79">
-        <v>3.391377266666666</v>
+        <v>3.137315066666664</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2800207188198952</v>
+        <v>0.2906671151298904</v>
       </c>
       <c r="T79">
-        <v>3.949297805849339</v>
+        <v>4.128811342478854</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.0706326079108807</v>
+        <v>0.069727061655613</v>
       </c>
       <c r="W79">
-        <v>0.1866169723314952</v>
+        <v>0.1867988060195529</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5650608632870456</v>
+        <v>0.5578164932449039</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2096498340238271</v>
+        <v>0.2111998340238271</v>
       </c>
       <c r="C80">
-        <v>-33.87267110646064</v>
+        <v>-35.87312929968449</v>
       </c>
       <c r="D80">
-        <v>78.12132889353936</v>
+        <v>77.5668707003155</v>
       </c>
       <c r="E80">
-        <v>-28.11200000000001</v>
+        <v>-26.66600000000001</v>
       </c>
       <c r="F80">
-        <v>112.788</v>
+        <v>114.234</v>
       </c>
       <c r="G80">
         <v>0.794</v>
@@ -7835,37 +7835,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M80">
-        <v>22.6478304</v>
+        <v>22.9381872</v>
       </c>
       <c r="N80">
-        <v>-10.01449706666667</v>
+        <v>-10.30485386666667</v>
       </c>
       <c r="O80">
-        <v>-1.251812133333334</v>
+        <v>-1.288106733333333</v>
       </c>
       <c r="P80">
-        <v>-8.762684933333336</v>
+        <v>-9.016747133333334</v>
       </c>
       <c r="Q80">
-        <v>3.137315066666664</v>
+        <v>2.883252866666666</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2906671151298904</v>
+        <v>0.3023274539455995</v>
       </c>
       <c r="T80">
-        <v>4.128811342478854</v>
+        <v>4.325421406406418</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.069727061655613</v>
+        <v>0.06884444062199765</v>
       </c>
       <c r="W80">
-        <v>0.1867988060195529</v>
+        <v>0.1869760363231029</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5578164932449039</v>
+        <v>0.5507555249759812</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2111998340238271</v>
+        <v>0.2127498340238272</v>
       </c>
       <c r="C81">
-        <v>-35.87312929968449</v>
+        <v>-37.86577253739496</v>
       </c>
       <c r="D81">
-        <v>77.5668707003155</v>
+        <v>77.02022746260505</v>
       </c>
       <c r="E81">
-        <v>-26.66600000000001</v>
+        <v>-25.22</v>
       </c>
       <c r="F81">
-        <v>114.234</v>
+        <v>115.68</v>
       </c>
       <c r="G81">
         <v>0.794</v>
@@ -7917,37 +7917,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M81">
-        <v>22.9381872</v>
+        <v>23.228544</v>
       </c>
       <c r="N81">
-        <v>-10.30485386666667</v>
+        <v>-10.59521066666667</v>
       </c>
       <c r="O81">
-        <v>-1.288106733333333</v>
+        <v>-1.324401333333334</v>
       </c>
       <c r="P81">
-        <v>-9.016747133333334</v>
+        <v>-9.270809333333338</v>
       </c>
       <c r="Q81">
-        <v>2.883252866666666</v>
+        <v>2.629190666666663</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3023274539455995</v>
+        <v>0.3151538266428795</v>
       </c>
       <c r="T81">
-        <v>4.325421406406418</v>
+        <v>4.54169247672674</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.06884444062199765</v>
+        <v>0.06798388511422267</v>
       </c>
       <c r="W81">
-        <v>0.1869760363231029</v>
+        <v>0.1871488358690641</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5507555249759812</v>
+        <v>0.5438710809137813</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2127498340238272</v>
+        <v>0.2142998340238272</v>
       </c>
       <c r="C82">
-        <v>-37.86577253739496</v>
+        <v>-39.85076488822887</v>
       </c>
       <c r="D82">
-        <v>77.02022746260505</v>
+        <v>76.48123511177114</v>
       </c>
       <c r="E82">
-        <v>-25.22</v>
+        <v>-23.774</v>
       </c>
       <c r="F82">
-        <v>115.68</v>
+        <v>117.126</v>
       </c>
       <c r="G82">
         <v>0.794</v>
@@ -7999,37 +7999,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M82">
-        <v>23.228544</v>
+        <v>23.5189008</v>
       </c>
       <c r="N82">
-        <v>-10.59521066666667</v>
+        <v>-10.88556746666667</v>
       </c>
       <c r="O82">
-        <v>-1.324401333333334</v>
+        <v>-1.360695933333334</v>
       </c>
       <c r="P82">
-        <v>-9.270809333333338</v>
+        <v>-9.524871533333336</v>
       </c>
       <c r="Q82">
-        <v>2.629190666666663</v>
+        <v>2.375128466666665</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3151538266428795</v>
+        <v>0.32933034383461</v>
       </c>
       <c r="T82">
-        <v>4.54169247672674</v>
+        <v>4.780728922870253</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.06798388511422267</v>
+        <v>0.06714457789059029</v>
       </c>
       <c r="W82">
-        <v>0.1871488358690641</v>
+        <v>0.1873173687595695</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5438710809137813</v>
+        <v>0.5371566231247223</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2142998340238272</v>
+        <v>0.2158498340238272</v>
       </c>
       <c r="C83">
-        <v>-39.85076488822887</v>
+        <v>-41.8282658600892</v>
       </c>
       <c r="D83">
-        <v>76.48123511177114</v>
+        <v>75.9497341399108</v>
       </c>
       <c r="E83">
-        <v>-23.774</v>
+        <v>-22.328</v>
       </c>
       <c r="F83">
-        <v>117.126</v>
+        <v>118.572</v>
       </c>
       <c r="G83">
         <v>0.794</v>
@@ -8081,37 +8081,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M83">
-        <v>23.5189008</v>
+        <v>23.8092576</v>
       </c>
       <c r="N83">
-        <v>-10.88556746666667</v>
+        <v>-11.17592426666667</v>
       </c>
       <c r="O83">
-        <v>-1.360695933333334</v>
+        <v>-1.396990533333334</v>
       </c>
       <c r="P83">
-        <v>-9.524871533333336</v>
+        <v>-9.778933733333337</v>
       </c>
       <c r="Q83">
-        <v>2.375128466666665</v>
+        <v>2.121066266666663</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.32933034383461</v>
+        <v>0.3450820296031994</v>
       </c>
       <c r="T83">
-        <v>4.780728922870253</v>
+        <v>5.046324974140822</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.06714457789059029</v>
+        <v>0.06632574157485138</v>
       </c>
       <c r="W83">
-        <v>0.1873173687595695</v>
+        <v>0.1874817910917699</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5371566231247223</v>
+        <v>0.5306059325988111</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2158498340238272</v>
+        <v>0.2173998340238271</v>
       </c>
       <c r="C84">
-        <v>-41.8282658600892</v>
+        <v>-43.79843055752391</v>
       </c>
       <c r="D84">
-        <v>75.9497341399108</v>
+        <v>75.42556944247609</v>
       </c>
       <c r="E84">
-        <v>-22.328</v>
+        <v>-20.88200000000001</v>
       </c>
       <c r="F84">
-        <v>118.572</v>
+        <v>120.018</v>
       </c>
       <c r="G84">
         <v>0.794</v>
@@ -8163,37 +8163,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M84">
-        <v>23.8092576</v>
+        <v>24.0996144</v>
       </c>
       <c r="N84">
-        <v>-11.17592426666667</v>
+        <v>-11.46628106666667</v>
       </c>
       <c r="O84">
-        <v>-1.396990533333334</v>
+        <v>-1.433285133333334</v>
       </c>
       <c r="P84">
-        <v>-9.778933733333337</v>
+        <v>-10.03299593333334</v>
       </c>
       <c r="Q84">
-        <v>2.121066266666663</v>
+        <v>1.867004066666665</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3450820296031994</v>
+        <v>0.3626868548739758</v>
       </c>
       <c r="T84">
-        <v>5.046324974140822</v>
+        <v>5.343167619678518</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.06632574157485138</v>
+        <v>0.06552663625467245</v>
       </c>
       <c r="W84">
-        <v>0.1874817910917699</v>
+        <v>0.1876422514400618</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5306059325988111</v>
+        <v>0.5242130900373796</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2173998340238271</v>
+        <v>0.2189498340238272</v>
       </c>
       <c r="C85">
-        <v>-43.79843055752391</v>
+        <v>-45.76140983263254</v>
       </c>
       <c r="D85">
-        <v>75.42556944247609</v>
+        <v>74.90859016736748</v>
       </c>
       <c r="E85">
-        <v>-20.88200000000001</v>
+        <v>-19.43599999999999</v>
       </c>
       <c r="F85">
-        <v>120.018</v>
+        <v>121.464</v>
       </c>
       <c r="G85">
         <v>0.794</v>
@@ -8245,37 +8245,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M85">
-        <v>24.0996144</v>
+        <v>24.38997120000001</v>
       </c>
       <c r="N85">
-        <v>-11.46628106666667</v>
+        <v>-11.75663786666667</v>
       </c>
       <c r="O85">
-        <v>-1.433285133333334</v>
+        <v>-1.469579733333334</v>
       </c>
       <c r="P85">
-        <v>-10.03299593333334</v>
+        <v>-10.28705813333334</v>
       </c>
       <c r="Q85">
-        <v>1.867004066666665</v>
+        <v>1.612941866666661</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3626868548739758</v>
+        <v>0.3824922833035995</v>
       </c>
       <c r="T85">
-        <v>5.343167619678518</v>
+        <v>5.677115595908427</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.06552663625467245</v>
+        <v>0.06474655725164062</v>
       </c>
       <c r="W85">
-        <v>0.1876422514400618</v>
+        <v>0.1877988913038706</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5242130900373796</v>
+        <v>0.5179724580131251</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2189498340238271</v>
+        <v>0.2204998340238271</v>
       </c>
       <c r="C86">
-        <v>-45.76140983263248</v>
+        <v>-47.71735042980873</v>
       </c>
       <c r="D86">
-        <v>74.90859016736751</v>
+        <v>74.39864957019127</v>
       </c>
       <c r="E86">
-        <v>-19.43600000000002</v>
+        <v>-17.99000000000001</v>
       </c>
       <c r="F86">
-        <v>121.464</v>
+        <v>122.91</v>
       </c>
       <c r="G86">
         <v>0.794</v>
@@ -8327,37 +8327,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M86">
-        <v>24.3899712</v>
+        <v>24.680328</v>
       </c>
       <c r="N86">
-        <v>-11.75663786666667</v>
+        <v>-12.04699466666667</v>
       </c>
       <c r="O86">
-        <v>-1.469579733333333</v>
+        <v>-1.505874333333334</v>
       </c>
       <c r="P86">
-        <v>-10.28705813333333</v>
+        <v>-10.54112033333334</v>
       </c>
       <c r="Q86">
-        <v>1.612941866666667</v>
+        <v>1.358879666666665</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3824922833035992</v>
+        <v>0.4049384355238391</v>
       </c>
       <c r="T86">
-        <v>5.677115595908423</v>
+        <v>6.055589968968984</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.06474655725164065</v>
+        <v>0.06398483304868016</v>
       </c>
       <c r="W86">
-        <v>0.1877988913038706</v>
+        <v>0.187951845523825</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5179724580131252</v>
+        <v>0.5118786643894413</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2204998340238271</v>
+        <v>0.2220498340238271</v>
       </c>
       <c r="C87">
-        <v>-47.71735042980873</v>
+        <v>-49.6663951246116</v>
       </c>
       <c r="D87">
-        <v>74.39864957019127</v>
+        <v>73.8956048753884</v>
       </c>
       <c r="E87">
-        <v>-17.99000000000001</v>
+        <v>-16.54400000000001</v>
       </c>
       <c r="F87">
-        <v>122.91</v>
+        <v>124.356</v>
       </c>
       <c r="G87">
         <v>0.794</v>
@@ -8409,37 +8409,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M87">
-        <v>24.680328</v>
+        <v>24.9706848</v>
       </c>
       <c r="N87">
-        <v>-12.04699466666667</v>
+        <v>-12.33735146666667</v>
       </c>
       <c r="O87">
-        <v>-1.505874333333334</v>
+        <v>-1.542168933333334</v>
       </c>
       <c r="P87">
-        <v>-10.54112033333334</v>
+        <v>-10.79518253333334</v>
       </c>
       <c r="Q87">
-        <v>1.358879666666665</v>
+        <v>1.104817466666665</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4049384355238391</v>
+        <v>0.4305911809183991</v>
       </c>
       <c r="T87">
-        <v>6.055589968968984</v>
+        <v>6.488132109609626</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.06398483304868016</v>
+        <v>0.0632408233620676</v>
       </c>
       <c r="W87">
-        <v>0.187951845523825</v>
+        <v>0.1881012426688968</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5118786643894413</v>
+        <v>0.5059265868965408</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2220498340238271</v>
+        <v>0.2235998340238272</v>
       </c>
       <c r="C88">
-        <v>-49.6663951246116</v>
+        <v>-51.60868285703992</v>
       </c>
       <c r="D88">
-        <v>73.8956048753884</v>
+        <v>73.39931714296007</v>
       </c>
       <c r="E88">
-        <v>-16.54400000000001</v>
+        <v>-15.09800000000001</v>
       </c>
       <c r="F88">
-        <v>124.356</v>
+        <v>125.802</v>
       </c>
       <c r="G88">
         <v>0.794</v>
@@ -8491,37 +8491,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M88">
-        <v>24.9706848</v>
+        <v>25.2610416</v>
       </c>
       <c r="N88">
-        <v>-12.33735146666667</v>
+        <v>-12.62770826666667</v>
       </c>
       <c r="O88">
-        <v>-1.542168933333334</v>
+        <v>-1.578463533333333</v>
       </c>
       <c r="P88">
-        <v>-10.79518253333334</v>
+        <v>-11.04924473333333</v>
       </c>
       <c r="Q88">
-        <v>1.104817466666665</v>
+        <v>0.8507552666666669</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4305911809183991</v>
+        <v>0.4601905025275068</v>
       </c>
       <c r="T88">
-        <v>6.488132109609626</v>
+        <v>6.987219194964213</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.0632408233620676</v>
+        <v>0.06251391734641165</v>
       </c>
       <c r="W88">
-        <v>0.1881012426688968</v>
+        <v>0.1882472053968405</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5059265868965408</v>
+        <v>0.5001113387712932</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2235998340238272</v>
+        <v>0.2564097303829952</v>
       </c>
       <c r="C89">
-        <v>-51.60868285703992</v>
+        <v>-62.19059335290953</v>
       </c>
       <c r="D89">
-        <v>73.39931714296007</v>
+        <v>64.26340664709046</v>
       </c>
       <c r="E89">
-        <v>-15.09800000000001</v>
+        <v>-13.65200000000002</v>
       </c>
       <c r="F89">
-        <v>125.802</v>
+        <v>127.248</v>
       </c>
       <c r="G89">
         <v>0.794</v>
@@ -8573,45 +8573,45 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M89">
-        <v>25.2610416</v>
+        <v>30.0050784</v>
       </c>
       <c r="N89">
-        <v>-12.62770826666667</v>
+        <v>-17.37174506666667</v>
       </c>
       <c r="O89">
-        <v>-1.578463533333333</v>
+        <v>-2.171468133333334</v>
       </c>
       <c r="P89">
-        <v>-11.04924473333333</v>
+        <v>-15.20027693333333</v>
       </c>
       <c r="Q89">
-        <v>0.8507552666666669</v>
+        <v>-3.300276933333334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4601905025275068</v>
+        <v>0.4985555140645332</v>
       </c>
       <c r="T89">
-        <v>6.987219194964213</v>
+        <v>7.634108405483079</v>
       </c>
       <c r="U89">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06251391734641165</v>
+        <v>0.05262997968592765</v>
       </c>
       <c r="W89">
-        <v>0.1882472053968405</v>
+        <v>0.2233898507900583</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.5001113387712932</v>
+        <v>0.4210398374874211</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2564097303829952</v>
+        <v>0.2583097303829953</v>
       </c>
       <c r="C90">
-        <v>-62.19059335290953</v>
+        <v>-64.09648252139844</v>
       </c>
       <c r="D90">
-        <v>64.26340664709046</v>
+        <v>63.80351747860154</v>
       </c>
       <c r="E90">
-        <v>-13.65200000000002</v>
+        <v>-12.20600000000002</v>
       </c>
       <c r="F90">
-        <v>127.248</v>
+        <v>128.694</v>
       </c>
       <c r="G90">
         <v>0.794</v>
@@ -8655,37 +8655,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M90">
-        <v>30.0050784</v>
+        <v>30.3460452</v>
       </c>
       <c r="N90">
-        <v>-17.37174506666667</v>
+        <v>-17.71271186666667</v>
       </c>
       <c r="O90">
-        <v>-2.171468133333334</v>
+        <v>-2.214088983333333</v>
       </c>
       <c r="P90">
-        <v>-15.20027693333333</v>
+        <v>-15.49862288333333</v>
       </c>
       <c r="Q90">
-        <v>-3.300276933333334</v>
+        <v>-3.598622883333332</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4985555140645332</v>
+        <v>0.5397151062522181</v>
       </c>
       <c r="T90">
-        <v>7.634108405483079</v>
+        <v>8.328118260526995</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05262997968592765</v>
+        <v>0.05203863159956891</v>
       </c>
       <c r="W90">
-        <v>0.2233898507900583</v>
+        <v>0.2235292906688217</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4210398374874211</v>
+        <v>0.4163090527965514</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2583097303829953</v>
+        <v>0.2602097303829953</v>
       </c>
       <c r="C91">
-        <v>-64.09648252139844</v>
+        <v>-65.99583623631912</v>
       </c>
       <c r="D91">
-        <v>63.80351747860154</v>
+        <v>63.35016376368087</v>
       </c>
       <c r="E91">
-        <v>-12.20600000000002</v>
+        <v>-10.76000000000002</v>
       </c>
       <c r="F91">
-        <v>128.694</v>
+        <v>130.14</v>
       </c>
       <c r="G91">
         <v>0.794</v>
@@ -8737,37 +8737,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M91">
-        <v>30.3460452</v>
+        <v>30.687012</v>
       </c>
       <c r="N91">
-        <v>-17.71271186666667</v>
+        <v>-18.05367866666667</v>
       </c>
       <c r="O91">
-        <v>-2.214088983333333</v>
+        <v>-2.256709833333334</v>
       </c>
       <c r="P91">
-        <v>-15.49862288333333</v>
+        <v>-15.79696883333334</v>
       </c>
       <c r="Q91">
-        <v>-3.598622883333332</v>
+        <v>-3.896968833333336</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5397151062522181</v>
+        <v>0.5891066168774399</v>
       </c>
       <c r="T91">
-        <v>8.328118260526995</v>
+        <v>9.160930086579697</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05203863159956891</v>
+        <v>0.05146042458179592</v>
       </c>
       <c r="W91">
-        <v>0.2235292906688217</v>
+        <v>0.2236656318836125</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4163090527965514</v>
+        <v>0.4116833966543673</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2602097303829953</v>
+        <v>0.2621097303829953</v>
       </c>
       <c r="C92">
-        <v>-65.99583623631912</v>
+        <v>-67.88879282710306</v>
       </c>
       <c r="D92">
-        <v>63.35016376368087</v>
+        <v>62.90320717289696</v>
       </c>
       <c r="E92">
-        <v>-10.76000000000002</v>
+        <v>-9.313999999999993</v>
       </c>
       <c r="F92">
-        <v>130.14</v>
+        <v>131.586</v>
       </c>
       <c r="G92">
         <v>0.794</v>
@@ -8819,37 +8819,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M92">
-        <v>30.687012</v>
+        <v>31.0279788</v>
       </c>
       <c r="N92">
-        <v>-18.05367866666667</v>
+        <v>-18.39464546666667</v>
       </c>
       <c r="O92">
-        <v>-2.256709833333334</v>
+        <v>-2.299330683333334</v>
       </c>
       <c r="P92">
-        <v>-15.79696883333334</v>
+        <v>-16.09531478333334</v>
       </c>
       <c r="Q92">
-        <v>-3.896968833333336</v>
+        <v>-4.195314783333339</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5891066168774399</v>
+        <v>0.649474018752711</v>
       </c>
       <c r="T92">
-        <v>9.160930086579697</v>
+        <v>10.17881120731077</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05146042458179592</v>
+        <v>0.05089492541056739</v>
       </c>
       <c r="W92">
-        <v>0.2236656318836125</v>
+        <v>0.2237989765881882</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4116833966543673</v>
+        <v>0.407159403284539</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2621097303829953</v>
+        <v>0.2640097303829952</v>
       </c>
       <c r="C93">
-        <v>-67.88879282710306</v>
+        <v>-69.77548674669004</v>
       </c>
       <c r="D93">
-        <v>62.90320717289696</v>
+        <v>62.46251325330999</v>
       </c>
       <c r="E93">
-        <v>-9.313999999999993</v>
+        <v>-7.867999999999995</v>
       </c>
       <c r="F93">
-        <v>131.586</v>
+        <v>133.032</v>
       </c>
       <c r="G93">
         <v>0.794</v>
@@ -8901,37 +8901,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M93">
-        <v>31.0279788</v>
+        <v>31.3689456</v>
       </c>
       <c r="N93">
-        <v>-18.39464546666667</v>
+        <v>-18.73561226666667</v>
       </c>
       <c r="O93">
-        <v>-2.299330683333334</v>
+        <v>-2.341951533333334</v>
       </c>
       <c r="P93">
-        <v>-16.09531478333334</v>
+        <v>-16.39366073333334</v>
       </c>
       <c r="Q93">
-        <v>-4.195314783333339</v>
+        <v>-4.493660733333337</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.649474018752711</v>
+        <v>0.7249332710968001</v>
       </c>
       <c r="T93">
-        <v>10.17881120731077</v>
+        <v>11.45116260822462</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05089492541056739</v>
+        <v>0.05034171969958296</v>
       </c>
       <c r="W93">
-        <v>0.2237989765881882</v>
+        <v>0.2239294224948383</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.407159403284539</v>
+        <v>0.4027337575966637</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2640097303829952</v>
+        <v>0.2659097303829953</v>
       </c>
       <c r="C94">
-        <v>-69.77548674669004</v>
+        <v>-71.65604870637523</v>
       </c>
       <c r="D94">
-        <v>62.46251325330999</v>
+        <v>62.02795129362479</v>
       </c>
       <c r="E94">
-        <v>-7.867999999999995</v>
+        <v>-6.421999999999997</v>
       </c>
       <c r="F94">
-        <v>133.032</v>
+        <v>134.478</v>
       </c>
       <c r="G94">
         <v>0.794</v>
@@ -8983,37 +8983,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M94">
-        <v>31.3689456</v>
+        <v>31.7099124</v>
       </c>
       <c r="N94">
-        <v>-18.73561226666667</v>
+        <v>-19.07657906666667</v>
       </c>
       <c r="O94">
-        <v>-2.341951533333334</v>
+        <v>-2.384572383333334</v>
       </c>
       <c r="P94">
-        <v>-16.39366073333334</v>
+        <v>-16.69200668333334</v>
       </c>
       <c r="Q94">
-        <v>-4.493660733333337</v>
+        <v>-4.792006683333339</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7249332710968001</v>
+        <v>0.8219523098249145</v>
       </c>
       <c r="T94">
-        <v>11.45116260822462</v>
+        <v>13.08704298082814</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05034171969958296</v>
+        <v>0.04980041088560895</v>
       </c>
       <c r="W94">
-        <v>0.2239294224948383</v>
+        <v>0.2240570631131734</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4027337575966637</v>
+        <v>0.3984032870848715</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2659097303829953</v>
+        <v>0.2678097303829953</v>
       </c>
       <c r="C95">
-        <v>-71.65604870637523</v>
+        <v>-73.53060580506599</v>
       </c>
       <c r="D95">
-        <v>62.02795129362479</v>
+        <v>61.59939419493402</v>
       </c>
       <c r="E95">
-        <v>-6.421999999999997</v>
+        <v>-4.975999999999999</v>
       </c>
       <c r="F95">
-        <v>134.478</v>
+        <v>135.924</v>
       </c>
       <c r="G95">
         <v>0.794</v>
@@ -9065,37 +9065,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M95">
-        <v>31.7099124</v>
+        <v>32.0508792</v>
       </c>
       <c r="N95">
-        <v>-19.07657906666667</v>
+        <v>-19.41754586666667</v>
       </c>
       <c r="O95">
-        <v>-2.384572383333334</v>
+        <v>-2.427193233333334</v>
       </c>
       <c r="P95">
-        <v>-16.69200668333334</v>
+        <v>-16.99035263333334</v>
       </c>
       <c r="Q95">
-        <v>-4.792006683333339</v>
+        <v>-5.090352633333337</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8219523098249145</v>
+        <v>0.9513110281290672</v>
       </c>
       <c r="T95">
-        <v>13.08704298082814</v>
+        <v>15.26821681096617</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04980041088560895</v>
+        <v>0.04927061928044289</v>
       </c>
       <c r="W95">
-        <v>0.2240570631131734</v>
+        <v>0.2241819879736716</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3984032870848715</v>
+        <v>0.3941649542435433</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2678097303829953</v>
+        <v>0.2697097303829953</v>
       </c>
       <c r="C96">
-        <v>-73.53060580506599</v>
+        <v>-75.39928165321727</v>
       </c>
       <c r="D96">
-        <v>61.59939419493402</v>
+        <v>61.17671834678274</v>
       </c>
       <c r="E96">
-        <v>-4.975999999999999</v>
+        <v>-3.530000000000001</v>
       </c>
       <c r="F96">
-        <v>135.924</v>
+        <v>137.37</v>
       </c>
       <c r="G96">
         <v>0.794</v>
@@ -9147,37 +9147,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M96">
-        <v>32.0508792</v>
+        <v>32.391846</v>
       </c>
       <c r="N96">
-        <v>-19.41754586666667</v>
+        <v>-19.75851266666667</v>
       </c>
       <c r="O96">
-        <v>-2.427193233333334</v>
+        <v>-2.469814083333334</v>
       </c>
       <c r="P96">
-        <v>-16.99035263333334</v>
+        <v>-17.28869858333334</v>
       </c>
       <c r="Q96">
-        <v>-5.090352633333337</v>
+        <v>-5.388698583333335</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9513110281290672</v>
+        <v>1.132413233754881</v>
       </c>
       <c r="T96">
-        <v>15.26821681096617</v>
+        <v>18.32186017315941</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04927061928044289</v>
+        <v>0.04875198118275403</v>
       </c>
       <c r="W96">
-        <v>0.2241819879736716</v>
+        <v>0.2243042828371066</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3941649542435433</v>
+        <v>0.3900158494620323</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2697097303829953</v>
+        <v>0.2716097303829953</v>
       </c>
       <c r="C97">
-        <v>-75.39928165321727</v>
+        <v>-77.26219649169937</v>
       </c>
       <c r="D97">
-        <v>61.17671834678274</v>
+        <v>60.75980350830064</v>
       </c>
       <c r="E97">
-        <v>-3.530000000000001</v>
+        <v>-2.084000000000003</v>
       </c>
       <c r="F97">
-        <v>137.37</v>
+        <v>138.816</v>
       </c>
       <c r="G97">
         <v>0.794</v>
@@ -9229,37 +9229,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M97">
-        <v>32.391846</v>
+        <v>32.7328128</v>
       </c>
       <c r="N97">
-        <v>-19.75851266666667</v>
+        <v>-20.09947946666667</v>
       </c>
       <c r="O97">
-        <v>-2.469814083333334</v>
+        <v>-2.512434933333334</v>
       </c>
       <c r="P97">
-        <v>-17.28869858333334</v>
+        <v>-17.58704453333334</v>
       </c>
       <c r="Q97">
-        <v>-5.388698583333335</v>
+        <v>-5.687044533333337</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.132413233754881</v>
+        <v>1.404066542193602</v>
       </c>
       <c r="T97">
-        <v>18.32186017315941</v>
+        <v>22.90232521644928</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04875198118275403</v>
+        <v>0.04824414804543367</v>
       </c>
       <c r="W97">
-        <v>0.2243042828371066</v>
+        <v>0.2244240298908868</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3900158494620323</v>
+        <v>0.3859531843634694</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2716097303829952</v>
+        <v>0.2735097303829953</v>
       </c>
       <c r="C98">
-        <v>-77.26219649169934</v>
+        <v>-79.11946730583811</v>
       </c>
       <c r="D98">
-        <v>60.75980350830066</v>
+        <v>60.34853269416189</v>
       </c>
       <c r="E98">
-        <v>-2.084000000000003</v>
+        <v>-0.6380000000000052</v>
       </c>
       <c r="F98">
-        <v>138.816</v>
+        <v>140.262</v>
       </c>
       <c r="G98">
         <v>0.794</v>
@@ -9311,37 +9311,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M98">
-        <v>32.7328128</v>
+        <v>33.0737796</v>
       </c>
       <c r="N98">
-        <v>-20.09947946666667</v>
+        <v>-20.44044626666667</v>
       </c>
       <c r="O98">
-        <v>-2.512434933333334</v>
+        <v>-2.555055783333334</v>
       </c>
       <c r="P98">
-        <v>-17.58704453333334</v>
+        <v>-17.88539048333334</v>
       </c>
       <c r="Q98">
-        <v>-5.687044533333337</v>
+        <v>-5.985390483333335</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.404066542193598</v>
+        <v>1.856822056258131</v>
       </c>
       <c r="T98">
-        <v>22.90232521644922</v>
+        <v>30.53643362193229</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04824414804543367</v>
+        <v>0.04774678569444982</v>
       </c>
       <c r="W98">
-        <v>0.2244240298908868</v>
+        <v>0.2245413079332488</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3859531843634694</v>
+        <v>0.3819742855555986</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2735097303829953</v>
+        <v>0.2754097303829953</v>
       </c>
       <c r="C99">
-        <v>-79.11946730583811</v>
+        <v>-80.97120793485469</v>
       </c>
       <c r="D99">
-        <v>60.34853269416189</v>
+        <v>59.94279206514531</v>
       </c>
       <c r="E99">
-        <v>-0.6380000000000052</v>
+        <v>0.8079999999999927</v>
       </c>
       <c r="F99">
-        <v>140.262</v>
+        <v>141.708</v>
       </c>
       <c r="G99">
         <v>0.794</v>
@@ -9393,37 +9393,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M99">
-        <v>33.0737796</v>
+        <v>33.4147464</v>
       </c>
       <c r="N99">
-        <v>-20.44044626666667</v>
+        <v>-20.78141306666667</v>
       </c>
       <c r="O99">
-        <v>-2.555055783333334</v>
+        <v>-2.597676633333333</v>
       </c>
       <c r="P99">
-        <v>-17.88539048333334</v>
+        <v>-18.18373643333333</v>
       </c>
       <c r="Q99">
-        <v>-5.985390483333335</v>
+        <v>-6.283736433333333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.856822056258131</v>
+        <v>2.762333084387197</v>
       </c>
       <c r="T99">
-        <v>30.53643362193229</v>
+        <v>45.80465043289843</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04774678569444982</v>
+        <v>0.04725957359552687</v>
       </c>
       <c r="W99">
-        <v>0.2245413079332488</v>
+        <v>0.2246561925461748</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3819742855555986</v>
+        <v>0.378076588764215</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2754097303829953</v>
+        <v>0.2773097303829953</v>
       </c>
       <c r="C100">
-        <v>-80.97120793485469</v>
+        <v>-82.8175291769202</v>
       </c>
       <c r="D100">
-        <v>59.94279206514531</v>
+        <v>59.5424708230798</v>
       </c>
       <c r="E100">
-        <v>0.8079999999999927</v>
+        <v>2.253999999999991</v>
       </c>
       <c r="F100">
-        <v>141.708</v>
+        <v>143.154</v>
       </c>
       <c r="G100">
         <v>0.794</v>
@@ -9475,37 +9475,37 @@
         <v>12.63333333333333</v>
       </c>
       <c r="M100">
-        <v>33.4147464</v>
+        <v>33.7557132</v>
       </c>
       <c r="N100">
-        <v>-20.78141306666667</v>
+        <v>-21.12237986666667</v>
       </c>
       <c r="O100">
-        <v>-2.597676633333333</v>
+        <v>-2.640297483333334</v>
       </c>
       <c r="P100">
-        <v>-18.18373643333333</v>
+        <v>-18.48208238333333</v>
       </c>
       <c r="Q100">
-        <v>-6.283736433333333</v>
+        <v>-6.582082383333335</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.762333084387197</v>
+        <v>5.478866168774394</v>
       </c>
       <c r="T100">
-        <v>45.80465043289843</v>
+        <v>91.60930086579687</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04725957359552687</v>
+        <v>0.04678220416526901</v>
       </c>
       <c r="W100">
-        <v>0.2246561925461748</v>
+        <v>0.2247687562578296</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.378076588764215</v>
+        <v>0.3742576333221522</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2773097303829953</v>
-      </c>
-      <c r="C101">
-        <v>-82.8175291769202</v>
-      </c>
-      <c r="D101">
-        <v>59.5424708230798</v>
-      </c>
-      <c r="E101">
-        <v>2.253999999999991</v>
-      </c>
-      <c r="F101">
-        <v>143.154</v>
-      </c>
-      <c r="G101">
-        <v>0.794</v>
-      </c>
-      <c r="H101">
-        <v>3.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>24.53333333333333</v>
-      </c>
-      <c r="K101">
-        <v>11.9</v>
-      </c>
-      <c r="L101">
-        <v>12.63333333333333</v>
-      </c>
-      <c r="M101">
-        <v>33.7557132</v>
-      </c>
-      <c r="N101">
-        <v>-21.12237986666667</v>
-      </c>
-      <c r="O101">
-        <v>-2.640297483333334</v>
-      </c>
-      <c r="P101">
-        <v>-18.48208238333333</v>
-      </c>
-      <c r="Q101">
-        <v>-6.582082383333335</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.478866168774394</v>
-      </c>
-      <c r="T101">
-        <v>91.60930086579687</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04678220416526901</v>
-      </c>
-      <c r="W101">
-        <v>0.2247687562578296</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3742576333221522</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
